--- a/Versão5/HIDS/Ontologia_HidroSanitaria.xlsx
+++ b/Versão5/HIDS/Ontologia_HidroSanitaria.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr codeName="EstaPastaDeTrabalho"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\HIDS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FBED982-19FD-4DE8-897E-04B30D0C84F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CAB4809-6E58-472F-AF9E-BD8C0A6DB551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -399,12 +399,6 @@
     <t>CTI_Projeto_01</t>
   </si>
   <si>
-    <t>fabricante</t>
-  </si>
-  <si>
-    <t>fornecedor</t>
-  </si>
-  <si>
     <t>código.abnt</t>
   </si>
   <si>
@@ -931,6 +925,12 @@
   </si>
   <si>
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
+  </si>
+  <si>
+    <t>quem.fabricou</t>
+  </si>
+  <si>
+    <t>quem.forneceu</t>
   </si>
 </sst>
 </file>
@@ -1483,14 +1483,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1554,46 +1546,6 @@
         <strike val="0"/>
         <color rgb="FFFFFFFF"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1778,6 +1730,54 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2305,7 +2305,7 @@
         <v>49</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C3" s="44" t="s">
         <v>94</v>
@@ -2461,7 +2461,7 @@
         <v>66</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C17" s="44" t="s">
         <v>94</v>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46139.497516203701</v>
+        <v>46213.807951388888</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>94</v>
@@ -2517,7 +2517,7 @@
         <v>72</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C22" s="44" t="s">
         <v>94</v>
@@ -2528,7 +2528,7 @@
         <v>73</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C23" s="44" t="s">
         <v>95</v>
@@ -2670,7 +2670,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C2" s="64" t="s">
         <v>84</v>
@@ -2679,10 +2679,10 @@
         <v>85</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F2" s="64" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G2" s="37" t="s">
         <v>9</v>
@@ -2716,7 +2716,7 @@
         <v>No Projeto</v>
       </c>
       <c r="P2" s="30" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="Q2" s="30" t="s">
         <v>86</v>
@@ -2737,7 +2737,7 @@
         <v>Definida</v>
       </c>
       <c r="V2" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W2" s="65" t="str">
         <f t="shared" ref="W2:W45" si="3">CONCATENATE("Key-HSA-",A2)</f>
@@ -2762,7 +2762,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C3" s="64" t="s">
         <v>84</v>
@@ -2771,10 +2771,10 @@
         <v>85</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F3" s="64" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G3" s="37" t="s">
         <v>9</v>
@@ -2808,7 +2808,7 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>86</v>
@@ -2829,7 +2829,7 @@
         <v>Requerida</v>
       </c>
       <c r="V3" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W3" s="65" t="str">
         <f t="shared" si="3"/>
@@ -2854,7 +2854,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C4" s="64" t="s">
         <v>84</v>
@@ -2863,10 +2863,10 @@
         <v>85</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F4" s="64" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G4" s="37" t="s">
         <v>9</v>
@@ -2900,7 +2900,7 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="30" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="Q4" s="30" t="s">
         <v>86</v>
@@ -2921,7 +2921,7 @@
         <v>Requerida</v>
       </c>
       <c r="V4" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W4" s="65" t="str">
         <f t="shared" si="3"/>
@@ -2946,7 +2946,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C5" s="64" t="s">
         <v>84</v>
@@ -2955,10 +2955,10 @@
         <v>85</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F5" s="64" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G5" s="37" t="s">
         <v>9</v>
@@ -2992,7 +2992,7 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="30" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="Q5" s="30" t="s">
         <v>86</v>
@@ -3013,7 +3013,7 @@
         <v>Requerida</v>
       </c>
       <c r="V5" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W5" s="65" t="str">
         <f t="shared" si="3"/>
@@ -3038,7 +3038,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C6" s="64" t="s">
         <v>84</v>
@@ -3047,10 +3047,10 @@
         <v>85</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F6" s="64" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G6" s="37" t="s">
         <v>9</v>
@@ -3084,7 +3084,7 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="30" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="Q6" s="30" t="s">
         <v>86</v>
@@ -3105,7 +3105,7 @@
         <v>Requerida</v>
       </c>
       <c r="V6" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W6" s="65" t="str">
         <f t="shared" si="3"/>
@@ -3133,16 +3133,16 @@
         <v>44</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D7" s="47" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E7" s="47" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F7" s="47" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G7" s="37" t="s">
         <v>9</v>
@@ -3176,39 +3176,39 @@
         <v>Sistema.ESG</v>
       </c>
       <c r="P7" s="58" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="Q7" s="58" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="R7" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S7" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T7" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U7" s="35" t="str">
         <f t="shared" ref="U7:U37" si="9">SUBSTITUTE(E7, "_", " ")</f>
         <v>Sistema.Sanitário</v>
       </c>
       <c r="V7" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W7" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-7</v>
       </c>
       <c r="X7" s="29" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Y7" s="29" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z7" s="34" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AA7" s="30" t="str">
         <f>_xlfn.TRANSLATE(P7,"pt","en")</f>
@@ -3223,16 +3223,16 @@
         <v>44</v>
       </c>
       <c r="C8" s="47" t="s">
+        <v>140</v>
+      </c>
+      <c r="D8" s="47" t="s">
+        <v>230</v>
+      </c>
+      <c r="E8" s="47" t="s">
         <v>142</v>
       </c>
-      <c r="D8" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="E8" s="47" t="s">
-        <v>144</v>
-      </c>
       <c r="F8" s="47" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G8" s="37" t="s">
         <v>9</v>
@@ -3266,39 +3266,39 @@
         <v>Sistema.AFR</v>
       </c>
       <c r="P8" s="58" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Q8" s="58" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="R8" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S8" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T8" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U8" s="35" t="str">
         <f t="shared" ref="U8:U17" si="13">SUBSTITUTE(E8, "_", " ")</f>
         <v>Sistema.Hidráulico</v>
       </c>
       <c r="V8" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W8" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-8</v>
       </c>
       <c r="X8" s="29" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Y8" s="29" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="Z8" s="34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA8" s="30" t="str">
         <f>_xlfn.TRANSLATE(P8,"pt","en")</f>
@@ -3313,16 +3313,16 @@
         <v>44</v>
       </c>
       <c r="C9" s="47" t="s">
+        <v>140</v>
+      </c>
+      <c r="D9" s="47" t="s">
+        <v>230</v>
+      </c>
+      <c r="E9" s="47" t="s">
         <v>142</v>
       </c>
-      <c r="D9" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="E9" s="47" t="s">
-        <v>144</v>
-      </c>
       <c r="F9" s="47" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G9" s="37" t="s">
         <v>9</v>
@@ -3356,39 +3356,39 @@
         <v>Sistema.AQT</v>
       </c>
       <c r="P9" s="58" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="Q9" s="58" t="s">
+        <v>165</v>
+      </c>
+      <c r="R9" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S9" s="35" t="s">
+        <v>168</v>
+      </c>
+      <c r="T9" s="35" t="s">
         <v>167</v>
-      </c>
-      <c r="R9" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S9" s="35" t="s">
-        <v>170</v>
-      </c>
-      <c r="T9" s="35" t="s">
-        <v>169</v>
       </c>
       <c r="U9" s="35" t="str">
         <f t="shared" si="13"/>
         <v>Sistema.Hidráulico</v>
       </c>
       <c r="V9" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W9" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-9</v>
       </c>
       <c r="X9" s="29" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Y9" s="29" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Z9" s="34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA9" s="30" t="str">
         <f>_xlfn.TRANSLATE(P9,"pt","en")</f>
@@ -3403,16 +3403,16 @@
         <v>44</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E10" s="47" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F10" s="47" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G10" s="37" t="s">
         <v>9</v>
@@ -3446,39 +3446,39 @@
         <v>Torneira</v>
       </c>
       <c r="P10" s="58" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="Q10" s="30" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="R10" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S10" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T10" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U10" s="35" t="str">
         <f t="shared" si="13"/>
         <v>Peças.Hidráulicas</v>
       </c>
       <c r="V10" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W10" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-10</v>
       </c>
       <c r="X10" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="Y10" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="Y10" s="29" t="s">
-        <v>202</v>
-      </c>
       <c r="Z10" s="34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA10" s="30" t="e" vm="1">
         <f t="shared" ref="AA10:AA17" si="14">_xlfn.TRANSLATE(P10,"pt","en")</f>
@@ -3493,16 +3493,16 @@
         <v>44</v>
       </c>
       <c r="C11" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E11" s="47" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F11" s="47" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G11" s="37" t="s">
         <v>9</v>
@@ -3536,7 +3536,7 @@
         <v>Misturador</v>
       </c>
       <c r="P11" s="58" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q11" s="30" t="str">
         <f t="shared" ref="Q11:Q17" si="15">_xlfn.TRANSLATE(P11,"pt","es")</f>
@@ -3546,30 +3546,30 @@
         <v>9</v>
       </c>
       <c r="S11" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T11" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U11" s="35" t="str">
         <f t="shared" si="13"/>
         <v>Peças.Hidráulicas</v>
       </c>
       <c r="V11" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W11" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-11</v>
       </c>
       <c r="X11" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="Y11" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="Y11" s="29" t="s">
-        <v>202</v>
-      </c>
       <c r="Z11" s="34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA11" s="30" t="str">
         <f t="shared" si="14"/>
@@ -3584,16 +3584,16 @@
         <v>44</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E12" s="47" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F12" s="47" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G12" s="37" t="s">
         <v>9</v>
@@ -3627,7 +3627,7 @@
         <v>Registro</v>
       </c>
       <c r="P12" s="58" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q12" s="30" t="str">
         <f t="shared" si="15"/>
@@ -3637,30 +3637,30 @@
         <v>9</v>
       </c>
       <c r="S12" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T12" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U12" s="35" t="str">
         <f t="shared" si="13"/>
         <v>Peças.Hidráulicas</v>
       </c>
       <c r="V12" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W12" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-12</v>
       </c>
       <c r="X12" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="Y12" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="Y12" s="29" t="s">
-        <v>202</v>
-      </c>
       <c r="Z12" s="34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA12" s="30" t="str">
         <f t="shared" si="14"/>
@@ -3675,16 +3675,16 @@
         <v>44</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E13" s="47" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F13" s="47" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G13" s="37" t="s">
         <v>9</v>
@@ -3718,7 +3718,7 @@
         <v>Válvula</v>
       </c>
       <c r="P13" s="58" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="Q13" s="30" t="str">
         <f t="shared" si="15"/>
@@ -3728,30 +3728,30 @@
         <v>9</v>
       </c>
       <c r="S13" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T13" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U13" s="35" t="str">
         <f t="shared" si="13"/>
         <v>Peças.Hidráulicas</v>
       </c>
       <c r="V13" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W13" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-13</v>
       </c>
       <c r="X13" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="Y13" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="Y13" s="29" t="s">
-        <v>202</v>
-      </c>
       <c r="Z13" s="34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA13" s="30" t="str">
         <f t="shared" si="14"/>
@@ -3766,16 +3766,16 @@
         <v>44</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F14" s="47" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G14" s="37" t="s">
         <v>9</v>
@@ -3809,7 +3809,7 @@
         <v>Chuveiro</v>
       </c>
       <c r="P14" s="58" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Q14" s="30" t="str">
         <f t="shared" si="15"/>
@@ -3819,30 +3819,30 @@
         <v>9</v>
       </c>
       <c r="S14" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T14" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U14" s="35" t="str">
         <f t="shared" ref="U14:U16" si="19">SUBSTITUTE(E14, "_", " ")</f>
         <v>Peças.Hidráulicas</v>
       </c>
       <c r="V14" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W14" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-14</v>
       </c>
       <c r="X14" s="29" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="Y14" s="29" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="Z14" s="34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA14" s="30" t="str">
         <f t="shared" ref="AA14:AA15" si="20">_xlfn.TRANSLATE(P14,"pt","en")</f>
@@ -3857,16 +3857,16 @@
         <v>44</v>
       </c>
       <c r="C15" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E15" s="47" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F15" s="47" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G15" s="37" t="s">
         <v>9</v>
@@ -3900,7 +3900,7 @@
         <v>Ducha</v>
       </c>
       <c r="P15" s="58" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="Q15" s="30" t="str">
         <f t="shared" ref="Q15" si="21">_xlfn.TRANSLATE(P15,"pt","es")</f>
@@ -3910,30 +3910,30 @@
         <v>9</v>
       </c>
       <c r="S15" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T15" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U15" s="35" t="str">
         <f t="shared" si="19"/>
         <v>Peças.Hidráulicas</v>
       </c>
       <c r="V15" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W15" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-15</v>
       </c>
       <c r="X15" s="29" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="Y15" s="29" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="Z15" s="34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA15" s="30" t="str">
         <f t="shared" si="20"/>
@@ -3948,16 +3948,16 @@
         <v>44</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E16" s="47" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F16" s="47" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G16" s="37" t="s">
         <v>9</v>
@@ -3991,42 +3991,42 @@
         <v>Medidor.de.Água</v>
       </c>
       <c r="P16" s="58" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="Q16" s="58" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="R16" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S16" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T16" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U16" s="35" t="str">
         <f t="shared" si="19"/>
         <v>Peças.Hidráulicas</v>
       </c>
       <c r="V16" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W16" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-16</v>
       </c>
       <c r="X16" s="29" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Y16" s="29" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="Z16" s="34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA16" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4037,16 +4037,16 @@
         <v>44</v>
       </c>
       <c r="C17" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E17" s="47" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F17" s="47" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G17" s="37" t="s">
         <v>9</v>
@@ -4080,7 +4080,7 @@
         <v>Acessório.Hidraúlico</v>
       </c>
       <c r="P17" s="58" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Q17" s="30" t="str">
         <f t="shared" si="15"/>
@@ -4090,30 +4090,30 @@
         <v>9</v>
       </c>
       <c r="S17" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T17" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U17" s="35" t="str">
         <f t="shared" si="13"/>
         <v>Peças.Hidráulicas</v>
       </c>
       <c r="V17" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W17" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-17</v>
       </c>
       <c r="X17" s="29" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="Y17" s="29" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="Z17" s="34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA17" s="30" t="str">
         <f t="shared" si="14"/>
@@ -4128,16 +4128,16 @@
         <v>44</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E18" s="47" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F18" s="47" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G18" s="37" t="s">
         <v>9</v>
@@ -4171,7 +4171,7 @@
         <v>Cisterna.Superior</v>
       </c>
       <c r="P18" s="58" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="Q18" s="30" t="str">
         <f>_xlfn.TRANSLATE(P18,"pt","es")</f>
@@ -4181,30 +4181,30 @@
         <v>9</v>
       </c>
       <c r="S18" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T18" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U18" s="35" t="str">
         <f t="shared" si="9"/>
         <v>Tubulação.Agua.Fria</v>
       </c>
       <c r="V18" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W18" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-18</v>
       </c>
       <c r="X18" s="29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y18" s="29" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="Z18" s="34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA18" s="30" t="str">
         <f t="shared" ref="AA18:AA32" si="22">_xlfn.TRANSLATE(P18,"pt","en")</f>
@@ -4219,16 +4219,16 @@
         <v>44</v>
       </c>
       <c r="C19" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E19" s="47" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F19" s="47" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G19" s="37" t="s">
         <v>9</v>
@@ -4262,7 +4262,7 @@
         <v>Cisterna.Intermediária</v>
       </c>
       <c r="P19" s="58" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="Q19" s="30" t="str">
         <f t="shared" ref="Q19:Q25" si="23">_xlfn.TRANSLATE(P19,"pt","es")</f>
@@ -4272,30 +4272,30 @@
         <v>9</v>
       </c>
       <c r="S19" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T19" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U19" s="35" t="str">
         <f t="shared" si="9"/>
         <v>Tubulação.Agua.Fria</v>
       </c>
       <c r="V19" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W19" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-19</v>
       </c>
       <c r="X19" s="29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y19" s="29" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="Z19" s="34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA19" s="30" t="str">
         <f t="shared" si="22"/>
@@ -4310,16 +4310,16 @@
         <v>44</v>
       </c>
       <c r="C20" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E20" s="47" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F20" s="47" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G20" s="37" t="s">
         <v>9</v>
@@ -4353,7 +4353,7 @@
         <v>Cisterna.Inferior</v>
       </c>
       <c r="P20" s="58" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Q20" s="30" t="str">
         <f t="shared" si="23"/>
@@ -4363,30 +4363,30 @@
         <v>9</v>
       </c>
       <c r="S20" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T20" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U20" s="35" t="str">
         <f t="shared" si="9"/>
         <v>Tubulação.Agua.Fria</v>
       </c>
       <c r="V20" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W20" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-20</v>
       </c>
       <c r="X20" s="29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y20" s="29" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="Z20" s="34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA20" s="30" t="str">
         <f t="shared" si="22"/>
@@ -4401,16 +4401,16 @@
         <v>44</v>
       </c>
       <c r="C21" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E21" s="47" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F21" s="47" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G21" s="37" t="s">
         <v>9</v>
@@ -4444,7 +4444,7 @@
         <v>Tubulação.AF</v>
       </c>
       <c r="P21" s="58" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Q21" s="30" t="str">
         <f t="shared" si="23"/>
@@ -4454,30 +4454,30 @@
         <v>9</v>
       </c>
       <c r="S21" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T21" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U21" s="35" t="str">
         <f t="shared" si="9"/>
         <v>Tubulação.Agua.Fria</v>
       </c>
       <c r="V21" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W21" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-21</v>
       </c>
       <c r="X21" s="29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y21" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Z21" s="34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA21" s="30" t="str">
         <f t="shared" si="22"/>
@@ -4492,16 +4492,16 @@
         <v>44</v>
       </c>
       <c r="C22" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E22" s="47" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F22" s="47" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G22" s="37" t="s">
         <v>9</v>
@@ -4535,39 +4535,39 @@
         <v>Aquecedor.de.Agua</v>
       </c>
       <c r="P22" s="58" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="Q22" s="30" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="R22" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S22" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T22" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U22" s="35" t="str">
         <f t="shared" si="9"/>
         <v>Tubulação.Agua.Quente</v>
       </c>
       <c r="V22" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W22" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-22</v>
       </c>
       <c r="X22" s="29" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="Y22" s="29" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="Z22" s="34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA22" s="30" t="str">
         <f t="shared" si="22"/>
@@ -4582,16 +4582,16 @@
         <v>44</v>
       </c>
       <c r="C23" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E23" s="47" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F23" s="47" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G23" s="37" t="s">
         <v>9</v>
@@ -4625,39 +4625,39 @@
         <v>Boiler</v>
       </c>
       <c r="P23" s="58" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Q23" s="30" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="R23" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S23" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T23" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U23" s="35" t="str">
         <f t="shared" si="9"/>
         <v>Tubulação.Agua.Quente</v>
       </c>
       <c r="V23" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W23" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-23</v>
       </c>
       <c r="X23" s="29" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="Y23" s="29" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="Z23" s="34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA23" s="30" t="str">
         <f t="shared" si="22"/>
@@ -4672,16 +4672,16 @@
         <v>44</v>
       </c>
       <c r="C24" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E24" s="47" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F24" s="47" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G24" s="37" t="s">
         <v>9</v>
@@ -4715,7 +4715,7 @@
         <v>Caldeira</v>
       </c>
       <c r="P24" s="58" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Q24" s="30" t="str">
         <f t="shared" si="23"/>
@@ -4725,30 +4725,30 @@
         <v>9</v>
       </c>
       <c r="S24" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T24" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U24" s="35" t="str">
         <f t="shared" si="9"/>
         <v>Tubulação.Agua.Quente</v>
       </c>
       <c r="V24" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W24" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-24</v>
       </c>
       <c r="X24" s="29" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="Y24" s="29" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="Z24" s="34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA24" s="30" t="str">
         <f t="shared" si="22"/>
@@ -4763,16 +4763,16 @@
         <v>44</v>
       </c>
       <c r="C25" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E25" s="47" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F25" s="47" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G25" s="37" t="s">
         <v>9</v>
@@ -4806,7 +4806,7 @@
         <v>Tubulação.AQ</v>
       </c>
       <c r="P25" s="58" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="Q25" s="30" t="str">
         <f t="shared" si="23"/>
@@ -4816,30 +4816,30 @@
         <v>9</v>
       </c>
       <c r="S25" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T25" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U25" s="35" t="str">
         <f t="shared" si="9"/>
         <v>Tubulação.Agua.Quente</v>
       </c>
       <c r="V25" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W25" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-25</v>
       </c>
       <c r="X25" s="29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y25" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Z25" s="34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA25" s="30" t="str">
         <f t="shared" si="22"/>
@@ -4854,16 +4854,16 @@
         <v>44</v>
       </c>
       <c r="C26" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E26" s="47" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F26" s="47" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G26" s="37" t="s">
         <v>9</v>
@@ -4897,39 +4897,39 @@
         <v>Tubulação.Reuso</v>
       </c>
       <c r="P26" s="58" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="Q26" s="58" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="R26" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S26" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T26" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U26" s="35" t="str">
         <f t="shared" si="9"/>
         <v>Tubulação.Agua.Quente</v>
       </c>
       <c r="V26" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W26" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-26</v>
       </c>
       <c r="X26" s="29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y26" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Z26" s="34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA26" s="30" t="str">
         <f t="shared" si="22"/>
@@ -4944,16 +4944,16 @@
         <v>44</v>
       </c>
       <c r="C27" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E27" s="47" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F27" s="47" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G27" s="37" t="s">
         <v>9</v>
@@ -4987,39 +4987,39 @@
         <v>Vaso.Sanitário</v>
       </c>
       <c r="P27" s="58" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="Q27" s="30" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="R27" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S27" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T27" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U27" s="35" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Sanitárias</v>
       </c>
       <c r="V27" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W27" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-27</v>
       </c>
       <c r="X27" s="29" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="Y27" s="29" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="Z27" s="34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA27" s="30" t="str">
         <f t="shared" si="22"/>
@@ -5034,16 +5034,16 @@
         <v>44</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E28" s="47" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F28" s="47" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G28" s="37" t="s">
         <v>9</v>
@@ -5077,7 +5077,7 @@
         <v>Bidet</v>
       </c>
       <c r="P28" s="58" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="Q28" s="30" t="str">
         <f t="shared" ref="Q28:Q32" si="24">_xlfn.TRANSLATE(P28,"pt","es")</f>
@@ -5087,30 +5087,30 @@
         <v>9</v>
       </c>
       <c r="S28" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T28" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U28" s="35" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Sanitárias</v>
       </c>
       <c r="V28" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W28" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-28</v>
       </c>
       <c r="X28" s="29" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="Y28" s="29" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="Z28" s="34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA28" s="30" t="str">
         <f t="shared" si="22"/>
@@ -5125,16 +5125,16 @@
         <v>44</v>
       </c>
       <c r="C29" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E29" s="47" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F29" s="47" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G29" s="37" t="s">
         <v>9</v>
@@ -5168,39 +5168,39 @@
         <v>Pia.Sanitária</v>
       </c>
       <c r="P29" s="58" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="Q29" s="30" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="R29" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S29" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T29" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U29" s="35" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Sanitárias</v>
       </c>
       <c r="V29" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W29" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-29</v>
       </c>
       <c r="X29" s="29" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="Y29" s="29" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="Z29" s="34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA29" s="30" t="str">
         <f t="shared" si="22"/>
@@ -5215,16 +5215,16 @@
         <v>44</v>
       </c>
       <c r="C30" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E30" s="47" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F30" s="47" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G30" s="37" t="s">
         <v>9</v>
@@ -5258,7 +5258,7 @@
         <v>Lavatório</v>
       </c>
       <c r="P30" s="58" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="Q30" s="30" t="str">
         <f t="shared" si="24"/>
@@ -5268,30 +5268,30 @@
         <v>9</v>
       </c>
       <c r="S30" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T30" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U30" s="35" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Sanitárias</v>
       </c>
       <c r="V30" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W30" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-30</v>
       </c>
       <c r="X30" s="29" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="Y30" s="29" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="Z30" s="34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA30" s="30" t="str">
         <f t="shared" si="22"/>
@@ -5306,16 +5306,16 @@
         <v>44</v>
       </c>
       <c r="C31" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E31" s="47" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F31" s="47" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G31" s="37" t="s">
         <v>9</v>
@@ -5349,39 +5349,39 @@
         <v>Cuba.Sanitária</v>
       </c>
       <c r="P31" s="58" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q31" s="30" t="s">
         <v>196</v>
       </c>
-      <c r="Q31" s="30" t="s">
-        <v>198</v>
-      </c>
       <c r="R31" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S31" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T31" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U31" s="35" t="str">
         <f t="shared" ref="U31" si="28">SUBSTITUTE(E31, "_", " ")</f>
         <v>Peças.Sanitárias</v>
       </c>
       <c r="V31" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W31" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-31</v>
       </c>
       <c r="X31" s="29" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="Y31" s="29" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="Z31" s="34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA31" s="30" t="str">
         <f t="shared" ref="AA31" si="29">_xlfn.TRANSLATE(P31,"pt","en")</f>
@@ -5396,16 +5396,16 @@
         <v>44</v>
       </c>
       <c r="C32" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E32" s="47" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F32" s="47" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G32" s="37" t="s">
         <v>9</v>
@@ -5439,7 +5439,7 @@
         <v>Banheira</v>
       </c>
       <c r="P32" s="58" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="Q32" s="30" t="str">
         <f t="shared" si="24"/>
@@ -5449,30 +5449,30 @@
         <v>9</v>
       </c>
       <c r="S32" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T32" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U32" s="35" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Sanitárias</v>
       </c>
       <c r="V32" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W32" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-32</v>
       </c>
       <c r="X32" s="29" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="Y32" s="29" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="Z32" s="34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA32" s="30" t="str">
         <f t="shared" si="22"/>
@@ -5487,16 +5487,16 @@
         <v>44</v>
       </c>
       <c r="C33" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E33" s="47" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F33" s="47" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G33" s="37" t="s">
         <v>9</v>
@@ -5530,39 +5530,39 @@
         <v>Ventilação.Esgoto</v>
       </c>
       <c r="P33" s="58" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Q33" s="58" t="s">
+        <v>166</v>
+      </c>
+      <c r="R33" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S33" s="35" t="s">
         <v>168</v>
       </c>
-      <c r="R33" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S33" s="35" t="s">
-        <v>170</v>
-      </c>
       <c r="T33" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U33" s="35" t="str">
         <f t="shared" ref="U33" si="33">SUBSTITUTE(E33, "_", " ")</f>
         <v>Esgoto.Coletores</v>
       </c>
       <c r="V33" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W33" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-33</v>
       </c>
       <c r="X33" s="29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y33" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Z33" s="34" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AA33" s="30" t="str">
         <f>_xlfn.TRANSLATE(P33,"pt","en")</f>
@@ -5577,16 +5577,16 @@
         <v>44</v>
       </c>
       <c r="C34" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E34" s="47" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F34" s="47" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G34" s="37" t="s">
         <v>9</v>
@@ -5620,39 +5620,39 @@
         <v>Ralo.Seco</v>
       </c>
       <c r="P34" s="58" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q34" s="30" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="R34" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S34" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T34" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U34" s="35" t="str">
         <f t="shared" si="9"/>
         <v>Esgoto.Coletores</v>
       </c>
       <c r="V34" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W34" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-34</v>
       </c>
       <c r="X34" s="29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y34" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Z34" s="34" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AA34" s="30" t="str">
         <f t="shared" ref="AA34:AA44" si="34">_xlfn.TRANSLATE(P34,"pt","en")</f>
@@ -5667,16 +5667,16 @@
         <v>44</v>
       </c>
       <c r="C35" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E35" s="47" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F35" s="47" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G35" s="37" t="s">
         <v>9</v>
@@ -5710,39 +5710,39 @@
         <v>Ralo.Sifonado</v>
       </c>
       <c r="P35" s="58" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="Q35" s="30" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="R35" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S35" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T35" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U35" s="35" t="str">
         <f t="shared" si="9"/>
         <v>Esgoto.Coletores</v>
       </c>
       <c r="V35" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W35" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-35</v>
       </c>
       <c r="X35" s="29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y35" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Z35" s="34" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AA35" s="30" t="str">
         <f t="shared" si="34"/>
@@ -5757,16 +5757,16 @@
         <v>44</v>
       </c>
       <c r="C36" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E36" s="47" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F36" s="47" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G36" s="37" t="s">
         <v>9</v>
@@ -5800,39 +5800,39 @@
         <v>Coletor.Andar</v>
       </c>
       <c r="P36" s="58" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q36" s="30" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="R36" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S36" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T36" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U36" s="35" t="str">
         <f t="shared" si="9"/>
         <v>Esgoto.Coletores</v>
       </c>
       <c r="V36" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W36" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-36</v>
       </c>
       <c r="X36" s="29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y36" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Z36" s="34" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AA36" s="30" t="str">
         <f t="shared" si="34"/>
@@ -5847,16 +5847,16 @@
         <v>44</v>
       </c>
       <c r="C37" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E37" s="47" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F37" s="47" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G37" s="37" t="s">
         <v>9</v>
@@ -5890,39 +5890,39 @@
         <v>Coletor.Predial</v>
       </c>
       <c r="P37" s="58" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="Q37" s="30" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="R37" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S37" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T37" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U37" s="35" t="str">
         <f t="shared" si="9"/>
         <v>Esgoto.Coletores</v>
       </c>
       <c r="V37" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W37" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-37</v>
       </c>
       <c r="X37" s="29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y37" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Z37" s="34" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AA37" s="30" t="str">
         <f t="shared" si="34"/>
@@ -5937,16 +5937,16 @@
         <v>44</v>
       </c>
       <c r="C38" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E38" s="47" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F38" s="47" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G38" s="37" t="s">
         <v>9</v>
@@ -5980,39 +5980,39 @@
         <v>Tubo.de.Queda</v>
       </c>
       <c r="P38" s="58" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="Q38" s="30" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="R38" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S38" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T38" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U38" s="35" t="str">
         <f t="shared" ref="U38" si="38">SUBSTITUTE(E38, "_", " ")</f>
         <v>Esgoto.Coletores</v>
       </c>
       <c r="V38" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W38" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-38</v>
       </c>
       <c r="X38" s="29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y38" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Z38" s="34" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AA38" s="30" t="str">
         <f t="shared" si="34"/>
@@ -6027,16 +6027,16 @@
         <v>44</v>
       </c>
       <c r="C39" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E39" s="47" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F39" s="47" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G39" s="37" t="s">
         <v>9</v>
@@ -6070,39 +6070,39 @@
         <v>Fecho.Hidráulico</v>
       </c>
       <c r="P39" s="58" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="Q39" s="30" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="R39" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S39" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T39" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U39" s="35" t="str">
         <f t="shared" ref="U39" si="42">SUBSTITUTE(E39, "_", " ")</f>
         <v>Esgoto.Coletores</v>
       </c>
       <c r="V39" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W39" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-39</v>
       </c>
       <c r="X39" s="29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y39" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Z39" s="34" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AA39" s="30" t="str">
         <f t="shared" si="34"/>
@@ -6117,16 +6117,16 @@
         <v>44</v>
       </c>
       <c r="C40" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E40" s="47" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F40" s="47" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G40" s="37" t="s">
         <v>9</v>
@@ -6160,39 +6160,39 @@
         <v>Caixa.de.Areia</v>
       </c>
       <c r="P40" s="58" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="Q40" s="30" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="R40" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S40" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T40" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U40" s="35" t="str">
         <f t="shared" ref="U40:U44" si="46">SUBSTITUTE(E40, "_", " ")</f>
         <v>Esgoto.Visitas</v>
       </c>
       <c r="V40" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W40" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-40</v>
       </c>
       <c r="X40" s="29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y40" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Z40" s="34" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AA40" s="30" t="str">
         <f t="shared" si="34"/>
@@ -6207,16 +6207,16 @@
         <v>44</v>
       </c>
       <c r="C41" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E41" s="47" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F41" s="47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G41" s="37" t="s">
         <v>9</v>
@@ -6250,39 +6250,39 @@
         <v>Caixa.de.Gordura</v>
       </c>
       <c r="P41" s="58" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="Q41" s="30" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="R41" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S41" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T41" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U41" s="35" t="str">
         <f t="shared" si="46"/>
         <v>Esgoto.Visitas</v>
       </c>
       <c r="V41" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W41" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-41</v>
       </c>
       <c r="X41" s="29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y41" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Z41" s="34" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AA41" s="30" t="str">
         <f t="shared" si="34"/>
@@ -6297,16 +6297,16 @@
         <v>44</v>
       </c>
       <c r="C42" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E42" s="47" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F42" s="47" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G42" s="37" t="s">
         <v>9</v>
@@ -6340,39 +6340,39 @@
         <v>Caixa.de.Inspeção</v>
       </c>
       <c r="P42" s="58" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="Q42" s="30" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="R42" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S42" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T42" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U42" s="35" t="str">
         <f t="shared" ref="U42:U43" si="50">SUBSTITUTE(E42, "_", " ")</f>
         <v>Esgoto.Visitas</v>
       </c>
       <c r="V42" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W42" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-42</v>
       </c>
       <c r="X42" s="29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y42" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Z42" s="34" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AA42" s="30" t="str">
         <f t="shared" si="34"/>
@@ -6387,16 +6387,16 @@
         <v>44</v>
       </c>
       <c r="C43" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E43" s="47" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F43" s="47" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G43" s="37" t="s">
         <v>9</v>
@@ -6430,39 +6430,39 @@
         <v>Caixa.Sifonada</v>
       </c>
       <c r="P43" s="58" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="Q43" s="30" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="R43" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S43" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T43" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U43" s="35" t="str">
         <f t="shared" si="50"/>
         <v>Esgoto.Visitas</v>
       </c>
       <c r="V43" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W43" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-43</v>
       </c>
       <c r="X43" s="29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y43" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Z43" s="34" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AA43" s="30" t="str">
         <f t="shared" si="34"/>
@@ -6477,16 +6477,16 @@
         <v>44</v>
       </c>
       <c r="C44" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E44" s="47" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F44" s="47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G44" s="37" t="s">
         <v>9</v>
@@ -6520,39 +6520,39 @@
         <v>Poço.de.Visita</v>
       </c>
       <c r="P44" s="58" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q44" s="30" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="R44" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S44" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T44" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U44" s="35" t="str">
         <f t="shared" si="46"/>
         <v>Esgoto.Visitas</v>
       </c>
       <c r="V44" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W44" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-44</v>
       </c>
       <c r="X44" s="29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y44" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Z44" s="34" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AA44" s="30" t="str">
         <f t="shared" si="34"/>
@@ -6567,16 +6567,16 @@
         <v>44</v>
       </c>
       <c r="C45" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E45" s="47" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F45" s="47" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G45" s="37" t="s">
         <v>9</v>
@@ -6610,39 +6610,39 @@
         <v>Acessório.Sanitário</v>
       </c>
       <c r="P45" s="58" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="Q45" s="58" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R45" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S45" s="35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T45" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U45" s="35" t="str">
         <f t="shared" ref="U45" si="54">SUBSTITUTE(E45, "_", " ")</f>
         <v>Esgoto.Acessórios</v>
       </c>
       <c r="V45" s="35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W45" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-HSA-45</v>
       </c>
       <c r="X45" s="29" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="Y45" s="29" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="Z45" s="34" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AA45" s="30" t="str">
         <f t="shared" ref="AA45" si="55">_xlfn.TRANSLATE(P45,"pt","en")</f>
@@ -6654,75 +6654,73 @@
     <sortCondition ref="F7:F936"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="F7:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="31" priority="15"/>
+  <conditionalFormatting sqref="A2:A45">
+    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
     <cfRule type="duplicateValues" dxfId="30" priority="1487"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="duplicateValues" dxfId="29" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:F1048576 F1">
+    <cfRule type="duplicateValues" dxfId="25" priority="15"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F16">
-    <cfRule type="duplicateValues" dxfId="29" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35">
-    <cfRule type="duplicateValues" dxfId="28" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F38 F40:F1048576 F17:F33 F1 F7:F15">
-    <cfRule type="duplicateValues" dxfId="27" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F46:F1048576">
-    <cfRule type="duplicateValues" dxfId="26" priority="244"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="246"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="1459"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="1480"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="244"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="246"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="1459"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1480"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:O1 A1:D1 Q1:X1 AA7:AA45">
-    <cfRule type="cellIs" dxfId="22" priority="51" operator="equal">
+  <conditionalFormatting sqref="F1:O1 A1:D1 Q1:X1">
+    <cfRule type="cellIs" dxfId="17" priority="51" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P7:P9">
-    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P10:P15 P17:P26">
-    <cfRule type="duplicateValues" dxfId="20" priority="1500"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1500"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P27:P32">
-    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P33">
-    <cfRule type="duplicateValues" dxfId="18" priority="1493"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="1493"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q7:Q9">
-    <cfRule type="duplicateValues" dxfId="17" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q26">
-    <cfRule type="duplicateValues" dxfId="16" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q33">
-    <cfRule type="duplicateValues" dxfId="15" priority="1494"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1494"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1:AA1">
-    <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="13" priority="6" operator="equal">
+  <conditionalFormatting sqref="AA2:AA45">
+    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A45">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -6937,7 +6935,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6964,9 +6962,9 @@
     <col min="7" max="7" width="56.3828125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.3046875" customWidth="1"/>
     <col min="9" max="9" width="19.3828125" customWidth="1"/>
-    <col min="10" max="10" width="4.69140625" customWidth="1"/>
+    <col min="10" max="10" width="5.84375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="4.765625" customWidth="1"/>
-    <col min="12" max="12" width="5.3046875" customWidth="1"/>
+    <col min="12" max="12" width="7.3828125" customWidth="1"/>
     <col min="13" max="13" width="18.4609375" customWidth="1"/>
     <col min="14" max="15" width="6.4609375" customWidth="1"/>
     <col min="16" max="16" width="5.3828125" customWidth="1"/>
@@ -7042,7 +7040,7 @@
         <v>100</v>
       </c>
       <c r="C2" s="59" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D2" s="56" t="s">
         <v>9</v>
@@ -7054,7 +7052,7 @@
         <v>78</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H2" s="55" t="s">
         <v>9</v>
@@ -7098,10 +7096,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D3" s="56" t="s">
         <v>83</v>
@@ -7113,13 +7111,13 @@
         <v>78</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H3" s="55" t="s">
         <v>78</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J3" s="55" t="s">
         <v>9</v>
@@ -7149,7 +7147,7 @@
         <v>9</v>
       </c>
       <c r="S3" s="24" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -7157,10 +7155,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D4" s="56" t="s">
         <v>83</v>
@@ -7172,13 +7170,13 @@
         <v>78</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H4" s="55" t="s">
         <v>78</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J4" s="55" t="s">
         <v>9</v>
@@ -7208,7 +7206,7 @@
         <v>9</v>
       </c>
       <c r="S4" s="24" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -7216,10 +7214,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D5" s="56" t="s">
         <v>83</v>
@@ -7231,13 +7229,13 @@
         <v>78</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H5" s="55" t="s">
         <v>78</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J5" s="55" t="s">
         <v>9</v>
@@ -7267,7 +7265,7 @@
         <v>9</v>
       </c>
       <c r="S5" s="24" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -7275,22 +7273,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="53" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D6" s="56" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F6" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H6" s="55" t="s">
         <v>9</v>
@@ -7299,34 +7297,34 @@
         <v>9</v>
       </c>
       <c r="J6" s="55" t="s">
+        <v>277</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="L6" s="55" t="s">
+        <v>278</v>
+      </c>
+      <c r="M6" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N6" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K6" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="L6" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M6" s="24" t="s">
+      <c r="O6" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="P6" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q6" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="R6" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N6" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O6" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="P6" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q6" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="R6" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S6" s="24" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -7334,22 +7332,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D7" s="56" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E7" s="38" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F7" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H7" s="55" t="s">
         <v>9</v>
@@ -7358,34 +7356,34 @@
         <v>9</v>
       </c>
       <c r="J7" s="55" t="s">
+        <v>277</v>
+      </c>
+      <c r="K7" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="L7" s="55" t="s">
+        <v>278</v>
+      </c>
+      <c r="M7" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N7" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K7" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="L7" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M7" s="24" t="s">
+      <c r="O7" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="P7" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q7" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="R7" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N7" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O7" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="P7" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q7" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="R7" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S7" s="24" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -7393,22 +7391,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D8" s="56" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E8" s="38" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F8" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H8" s="55" t="s">
         <v>9</v>
@@ -7417,34 +7415,34 @@
         <v>9</v>
       </c>
       <c r="J8" s="55" t="s">
+        <v>277</v>
+      </c>
+      <c r="K8" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="L8" s="55" t="s">
+        <v>278</v>
+      </c>
+      <c r="M8" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N8" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K8" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="L8" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M8" s="24" t="s">
+      <c r="O8" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="P8" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q8" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="R8" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N8" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O8" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="P8" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q8" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="R8" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S8" s="24" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -7452,22 +7450,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E9" s="38" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F9" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H9" s="55" t="s">
         <v>9</v>
@@ -7476,34 +7474,34 @@
         <v>9</v>
       </c>
       <c r="J9" s="55" t="s">
+        <v>277</v>
+      </c>
+      <c r="K9" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="L9" s="55" t="s">
+        <v>278</v>
+      </c>
+      <c r="M9" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N9" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K9" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="L9" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M9" s="24" t="s">
+      <c r="O9" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="P9" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q9" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="R9" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N9" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O9" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="P9" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q9" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="R9" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S9" s="24" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -7511,22 +7509,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="53" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D10" s="56" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E10" s="38" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F10" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H10" s="55" t="s">
         <v>9</v>
@@ -7535,34 +7533,34 @@
         <v>9</v>
       </c>
       <c r="J10" s="55" t="s">
+        <v>277</v>
+      </c>
+      <c r="K10" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="L10" s="55" t="s">
+        <v>278</v>
+      </c>
+      <c r="M10" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N10" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K10" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="L10" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M10" s="24" t="s">
+      <c r="O10" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="P10" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q10" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="R10" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N10" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O10" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="P10" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q10" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="R10" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S10" s="24" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -7570,22 +7568,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="53" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C11" s="47" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D11" s="56" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E11" s="38" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F11" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H11" s="55" t="s">
         <v>9</v>
@@ -7594,34 +7592,34 @@
         <v>9</v>
       </c>
       <c r="J11" s="55" t="s">
+        <v>277</v>
+      </c>
+      <c r="K11" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="L11" s="55" t="s">
+        <v>278</v>
+      </c>
+      <c r="M11" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N11" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K11" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="L11" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M11" s="24" t="s">
+      <c r="O11" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="P11" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q11" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="R11" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N11" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O11" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="P11" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q11" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="R11" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S11" s="24" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -7629,22 +7627,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="53" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D12" s="56" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F12" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H12" s="55" t="s">
         <v>9</v>
@@ -7653,34 +7651,34 @@
         <v>9</v>
       </c>
       <c r="J12" s="55" t="s">
+        <v>277</v>
+      </c>
+      <c r="K12" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="L12" s="55" t="s">
+        <v>278</v>
+      </c>
+      <c r="M12" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N12" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K12" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="L12" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M12" s="24" t="s">
+      <c r="O12" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="P12" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q12" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="R12" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N12" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O12" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="P12" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q12" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="R12" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S12" s="24" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -7688,22 +7686,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="53" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D13" s="56" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E13" s="38" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F13" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H13" s="55" t="s">
         <v>9</v>
@@ -7712,34 +7710,34 @@
         <v>9</v>
       </c>
       <c r="J13" s="55" t="s">
+        <v>277</v>
+      </c>
+      <c r="K13" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="L13" s="55" t="s">
+        <v>278</v>
+      </c>
+      <c r="M13" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N13" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K13" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="L13" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M13" s="24" t="s">
+      <c r="O13" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="P13" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q13" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="R13" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N13" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O13" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="P13" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q13" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="R13" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S13" s="24" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -7747,22 +7745,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="53" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D14" s="56" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F14" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H14" s="55" t="s">
         <v>9</v>
@@ -7771,34 +7769,34 @@
         <v>9</v>
       </c>
       <c r="J14" s="55" t="s">
+        <v>277</v>
+      </c>
+      <c r="K14" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="L14" s="55" t="s">
+        <v>278</v>
+      </c>
+      <c r="M14" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N14" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K14" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="L14" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M14" s="24" t="s">
+      <c r="O14" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="P14" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q14" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="R14" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N14" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O14" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="P14" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q14" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="R14" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S14" s="24" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -7806,22 +7804,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="53" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C15" s="47" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D15" s="56" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E15" s="38" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F15" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H15" s="55" t="s">
         <v>9</v>
@@ -7830,34 +7828,34 @@
         <v>9</v>
       </c>
       <c r="J15" s="55" t="s">
+        <v>277</v>
+      </c>
+      <c r="K15" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="L15" s="55" t="s">
+        <v>278</v>
+      </c>
+      <c r="M15" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N15" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K15" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="L15" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M15" s="24" t="s">
+      <c r="O15" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="P15" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q15" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="R15" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N15" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O15" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="P15" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q15" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="R15" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S15" s="24" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -7865,22 +7863,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="53" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D16" s="56" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F16" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H16" s="55" t="s">
         <v>9</v>
@@ -7889,34 +7887,34 @@
         <v>9</v>
       </c>
       <c r="J16" s="55" t="s">
+        <v>277</v>
+      </c>
+      <c r="K16" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="L16" s="55" t="s">
+        <v>278</v>
+      </c>
+      <c r="M16" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N16" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K16" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="L16" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M16" s="24" t="s">
+      <c r="O16" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="P16" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q16" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="R16" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N16" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O16" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="P16" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q16" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="R16" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S16" s="24" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -7924,22 +7922,22 @@
         <v>16</v>
       </c>
       <c r="B17" s="53" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C17" s="47" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D17" s="56" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F17" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H17" s="55" t="s">
         <v>9</v>
@@ -7948,34 +7946,34 @@
         <v>9</v>
       </c>
       <c r="J17" s="55" t="s">
+        <v>277</v>
+      </c>
+      <c r="K17" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="L17" s="55" t="s">
+        <v>278</v>
+      </c>
+      <c r="M17" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N17" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K17" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="L17" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M17" s="24" t="s">
+      <c r="O17" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="P17" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q17" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="R17" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N17" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O17" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="P17" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q17" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="R17" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S17" s="24" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -7983,22 +7981,22 @@
         <v>17</v>
       </c>
       <c r="B18" s="53" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D18" s="56" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E18" s="38" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F18" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H18" s="55" t="s">
         <v>9</v>
@@ -8007,34 +8005,34 @@
         <v>9</v>
       </c>
       <c r="J18" s="55" t="s">
+        <v>277</v>
+      </c>
+      <c r="K18" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="L18" s="55" t="s">
+        <v>278</v>
+      </c>
+      <c r="M18" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N18" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K18" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="L18" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M18" s="24" t="s">
+      <c r="O18" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="P18" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q18" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="R18" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N18" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O18" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="P18" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q18" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="R18" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S18" s="24" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -8042,22 +8040,22 @@
         <v>18</v>
       </c>
       <c r="B19" s="53" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C19" s="47" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D19" s="56" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E19" s="38" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F19" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G19" s="23" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H19" s="55" t="s">
         <v>9</v>
@@ -8066,40 +8064,40 @@
         <v>9</v>
       </c>
       <c r="J19" s="55" t="s">
+        <v>277</v>
+      </c>
+      <c r="K19" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="L19" s="55" t="s">
+        <v>278</v>
+      </c>
+      <c r="M19" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N19" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K19" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="L19" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M19" s="24" t="s">
+      <c r="O19" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="P19" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q19" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="R19" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N19" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O19" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="P19" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q19" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="R19" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S19" s="24" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3:C5">
-    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8169,22 +8167,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="5" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/HIDS/Ontologia_HidroSanitaria.xlsx
+++ b/Versão5/HIDS/Ontologia_HidroSanitaria.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\HIDS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CAB4809-6E58-472F-AF9E-BD8C0A6DB551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B2DCE1-548C-4F34-B99A-358A9A635FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46213.807951388888</v>
+        <v>46214.37796863426</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>94</v>
@@ -6953,24 +6953,25 @@
   <dimension ref="A1:S19"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.85" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.69140625" customWidth="1"/>
-    <col min="3" max="3" width="9.69140625" customWidth="1"/>
-    <col min="4" max="4" width="7.07421875" customWidth="1"/>
-    <col min="5" max="5" width="7.4609375" customWidth="1"/>
-    <col min="6" max="6" width="4.61328125" customWidth="1"/>
+    <col min="1" max="1" width="1.765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.23046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.53515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.23046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.53515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.07421875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="56.3828125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.3046875" customWidth="1"/>
-    <col min="9" max="9" width="19.3828125" customWidth="1"/>
+    <col min="8" max="8" width="4.07421875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.07421875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.84375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.765625" customWidth="1"/>
-    <col min="12" max="12" width="7.3828125" customWidth="1"/>
-    <col min="13" max="13" width="18.4609375" customWidth="1"/>
-    <col min="14" max="15" width="6.4609375" customWidth="1"/>
-    <col min="16" max="16" width="5.3828125" customWidth="1"/>
-    <col min="17" max="17" width="14.53515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.765625" customWidth="1"/>
-    <col min="19" max="19" width="18.3046875" customWidth="1"/>
+    <col min="11" max="11" width="3.23046875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.15234375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.15234375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.921875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.765625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="3.921875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.15234375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.765625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.23046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="14.6" customHeight="1" x14ac:dyDescent="0.4">

--- a/Versão5/HIDS/Ontologia_HidroSanitaria.xlsx
+++ b/Versão5/HIDS/Ontologia_HidroSanitaria.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\HIDS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B2DCE1-548C-4F34-B99A-358A9A635FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56016967-CD35-4586-AD00-F73F19195B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="278">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -225,9 +225,6 @@
     <t>000 Traducción Classe 5</t>
   </si>
   <si>
-    <t>Projeto</t>
-  </si>
-  <si>
     <t>Chave</t>
   </si>
   <si>
@@ -888,18 +885,9 @@
     <t>[ OST_PipeFitting ]</t>
   </si>
   <si>
-    <t>Definida</t>
-  </si>
-  <si>
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Definição do Projeto.</t>
   </si>
   <si>
-    <t>Requerida</t>
-  </si>
-  <si>
-    <t>No.Projeto</t>
-  </si>
-  <si>
     <t>Gestão</t>
   </si>
   <si>
@@ -931,6 +919,15 @@
   </si>
   <si>
     <t>quem.forneceu</t>
+  </si>
+  <si>
+    <t>Conceito</t>
+  </si>
+  <si>
+    <t>Contêineres</t>
+  </si>
+  <si>
+    <t>[ 5I ]</t>
   </si>
 </sst>
 </file>
@@ -1273,7 +1270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1372,18 +1369,6 @@
     <xf numFmtId="0" fontId="2" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1408,9 +1393,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1422,9 +1404,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1465,14 +1444,87 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="32">
+  <dxfs count="39">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2270,280 +2322,280 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.69140625" style="62" customWidth="1"/>
-    <col min="2" max="2" width="40.07421875" style="62" customWidth="1"/>
-    <col min="3" max="3" width="3.4609375" style="45" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="62"/>
+    <col min="1" max="1" width="8.7109375" style="56" customWidth="1"/>
+    <col min="2" max="2" width="40.140625" style="56" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="56"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="C1" s="39" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="B2" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="40" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" s="13" t="s">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="13" t="s">
+      <c r="B3" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
         <v>49</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="C3" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="14" t="s">
-        <v>50</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C4" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B5" s="14" t="str">
         <f>_xlfn.CONCAT(B4,"Prop")</f>
         <v>BIMProp</v>
       </c>
-      <c r="C5" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C5" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" s="14" t="str">
         <f>_xlfn.CONCAT(B4,"Data")</f>
         <v>BIMData</v>
       </c>
-      <c r="C6" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C6" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="C7" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="42" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="41" t="s">
+      <c r="B8" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="41" t="s">
-        <v>91</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="14" t="s">
+      <c r="B9" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="C9" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="14" t="s">
+      <c r="B10" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="C10" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="14" t="s">
+      <c r="B11" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="14" t="s">
+      <c r="B12" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="14" t="s">
+      <c r="B13" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="14" t="s">
+      <c r="B14" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="14" t="s">
+      <c r="B15" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="14" t="s">
+      <c r="B16" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="14" t="s">
+      <c r="B17" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="C17" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
         <v>66</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="C17" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="14" t="s">
-        <v>67</v>
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46214.37796863426</v>
-      </c>
-      <c r="C18" s="44" t="s">
+        <v>46216.386411574073</v>
+      </c>
+      <c r="C18" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="C22" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="C23" s="40" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="C22" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="C23" s="44" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="42" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B24" s="16" t="str">
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Formalize elements of the BIM project. Specific Objects of Hydraulics and Sanitary Sewer</v>
       </c>
-      <c r="C24" s="44" t="s">
-        <v>96</v>
+      <c r="C24" s="40" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -2555,153 +2607,154 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA45"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.84375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.3828125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.84375" customWidth="1"/>
-    <col min="4" max="4" width="10.3046875" customWidth="1"/>
-    <col min="5" max="5" width="10.15234375" customWidth="1"/>
-    <col min="6" max="6" width="9.84375" style="46" customWidth="1"/>
-    <col min="7" max="11" width="6.3046875" style="36" customWidth="1"/>
-    <col min="12" max="12" width="7.4609375" customWidth="1"/>
-    <col min="13" max="13" width="10.15234375" customWidth="1"/>
-    <col min="14" max="14" width="11" customWidth="1"/>
-    <col min="15" max="15" width="10.3828125" customWidth="1"/>
-    <col min="16" max="16" width="32.07421875" customWidth="1"/>
-    <col min="17" max="17" width="30.53515625" customWidth="1"/>
-    <col min="18" max="18" width="3.84375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.921875" customWidth="1"/>
-    <col min="20" max="20" width="5.69140625" customWidth="1"/>
-    <col min="21" max="21" width="10.53515625" customWidth="1"/>
-    <col min="22" max="22" width="5.61328125" customWidth="1"/>
-    <col min="23" max="23" width="6.3046875" style="60" customWidth="1"/>
-    <col min="24" max="24" width="52.3046875" style="60" customWidth="1"/>
-    <col min="25" max="25" width="19.23046875" style="61" customWidth="1"/>
-    <col min="26" max="26" width="5.61328125" style="36" customWidth="1"/>
-    <col min="27" max="27" width="31.15234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="54" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" style="54" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" style="62" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8" style="54" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.85546875" style="54" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.28515625" style="54" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="64.5703125" style="54" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="41" style="54" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.85546875" style="54" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.85546875" style="54" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.28515625" style="54" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.5703125" style="54" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="43.85546875" style="54" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="19.28515625" style="55" customWidth="1"/>
+    <col min="26" max="26" width="7.28515625" style="54" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="67.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="48" t="s">
+    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="49" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="49" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="49" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="49" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="50" t="s">
+      <c r="M1" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q1" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>98</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="T1" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="U1" s="46" t="s">
+        <v>35</v>
+      </c>
+      <c r="V1" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="W1" s="57" t="s">
+        <v>8</v>
+      </c>
+      <c r="X1" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y1" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z1" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA1" s="36" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="59">
         <v>2</v>
       </c>
-      <c r="J1" s="50" t="s">
-        <v>3</v>
-      </c>
-      <c r="K1" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="M1" s="39" t="s">
-        <v>5</v>
-      </c>
-      <c r="N1" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="O1" s="39" t="s">
-        <v>7</v>
-      </c>
-      <c r="P1" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q1" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="R1" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="S1" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="T1" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="U1" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="V1" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="W1" s="63" t="s">
-        <v>8</v>
-      </c>
-      <c r="X1" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y1" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="Z1" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="AA1" s="40" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="32">
-        <v>2</v>
-      </c>
       <c r="B2" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="C2" s="64" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="F2" s="64" t="s">
-        <v>267</v>
-      </c>
-      <c r="G2" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="37" t="s">
+      <c r="E2" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="F2" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="G2" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L2" s="33" t="str">
         <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M2" s="33" t="str">
         <f t="shared" si="0"/>
@@ -2709,39 +2762,39 @@
       </c>
       <c r="N2" s="33" t="str">
         <f t="shared" ref="N2:O6" si="1">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
-        <v>Definida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O2" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>No Projeto</v>
+        <v>Contêiner</v>
       </c>
       <c r="P2" s="30" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Q2" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="R2" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="35" t="str">
+        <v>85</v>
+      </c>
+      <c r="R2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="30" t="str">
         <f t="shared" ref="S2:U6" si="2">SUBSTITUTE(C2, ".", " ")</f>
-        <v>Contêiner</v>
-      </c>
-      <c r="T2" s="35" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T2" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U2" s="35" t="str">
+      <c r="U2" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Definida</v>
-      </c>
-      <c r="V2" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W2" s="65" t="str">
-        <f t="shared" ref="W2:W45" si="3">CONCATENATE("Key-HSA-",A2)</f>
-        <v>Key-HSA-2</v>
+        <v>Contêineres</v>
+      </c>
+      <c r="V2" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W2" s="60" t="str">
+        <f>CONCATENATE("Key-HIDR-",A2)</f>
+        <v>Key-HIDR-2</v>
       </c>
       <c r="X2" s="30" t="s">
         <v>9</v>
@@ -2749,51 +2802,51 @@
       <c r="Y2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="Z2" s="34" t="s">
-        <v>9</v>
+      <c r="Z2" s="30" t="s">
+        <v>277</v>
       </c>
       <c r="AA2" s="30" t="str">
-        <f t="shared" ref="AA2:AA6" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
+        <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="32">
+    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="59">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="C3" s="64" t="s">
+        <v>275</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="F3" s="64" t="s">
-        <v>269</v>
-      </c>
-      <c r="G3" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="37" t="s">
+      <c r="E3" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="F3" s="58" t="s">
+        <v>265</v>
+      </c>
+      <c r="G3" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L3" s="33" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M3" s="33" t="str">
         <f t="shared" si="0"/>
@@ -2801,91 +2854,91 @@
       </c>
       <c r="N3" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O3" s="33" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="Q3" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="R3" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S3" s="35" t="str">
+        <v>85</v>
+      </c>
+      <c r="R3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S3" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T3" s="35" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T3" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U3" s="35" t="str">
+      <c r="U3" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V3" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W3" s="65" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="V3" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W3" s="60" t="str">
+        <f t="shared" ref="W3:W45" si="4">CONCATENATE("Key-HIDR-",A3)</f>
+        <v>Key-HIDR-3</v>
+      </c>
+      <c r="X3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA3" s="30" t="str">
         <f t="shared" si="3"/>
-        <v>Key-HSA-3</v>
-      </c>
-      <c r="X3" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y3" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z3" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA3" s="30" t="str">
-        <f t="shared" si="4"/>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="32">
+    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="59">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="C4" s="64" t="s">
+        <v>275</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="F4" s="64" t="s">
-        <v>271</v>
-      </c>
-      <c r="G4" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="37" t="s">
+      <c r="E4" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="F4" s="58" t="s">
+        <v>267</v>
+      </c>
+      <c r="G4" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L4" s="33" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M4" s="33" t="str">
         <f t="shared" si="0"/>
@@ -2893,91 +2946,91 @@
       </c>
       <c r="N4" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O4" s="33" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="30" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="Q4" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="R4" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S4" s="35" t="str">
+        <v>85</v>
+      </c>
+      <c r="R4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S4" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T4" s="35" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T4" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U4" s="35" t="str">
+      <c r="U4" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V4" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W4" s="65" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="V4" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W4" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-4</v>
+      </c>
+      <c r="X4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA4" s="30" t="str">
         <f t="shared" si="3"/>
-        <v>Key-HSA-4</v>
-      </c>
-      <c r="X4" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y4" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z4" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA4" s="30" t="str">
-        <f t="shared" si="4"/>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="32">
+    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="59">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="C5" s="64" t="s">
+        <v>275</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="F5" s="64" t="s">
-        <v>273</v>
-      </c>
-      <c r="G5" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="37" t="s">
+      <c r="E5" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="F5" s="58" t="s">
+        <v>269</v>
+      </c>
+      <c r="G5" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L5" s="33" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M5" s="33" t="str">
         <f t="shared" si="0"/>
@@ -2985,91 +3038,91 @@
       </c>
       <c r="N5" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O5" s="33" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="30" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="Q5" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="R5" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S5" s="35" t="str">
+        <v>85</v>
+      </c>
+      <c r="R5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S5" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T5" s="35" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T5" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U5" s="35" t="str">
+      <c r="U5" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V5" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W5" s="65" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="V5" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W5" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-5</v>
+      </c>
+      <c r="X5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA5" s="30" t="str">
         <f t="shared" si="3"/>
-        <v>Key-HSA-5</v>
-      </c>
-      <c r="X5" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y5" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z5" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA5" s="30" t="str">
-        <f t="shared" si="4"/>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="32">
+    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="59">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="C6" s="64" t="s">
+        <v>275</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="F6" s="64" t="s">
-        <v>275</v>
-      </c>
-      <c r="G6" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="37" t="s">
+      <c r="E6" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="F6" s="58" t="s">
+        <v>271</v>
+      </c>
+      <c r="G6" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L6" s="33" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M6" s="33" t="str">
         <f t="shared" si="0"/>
@@ -3077,86 +3130,86 @@
       </c>
       <c r="N6" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O6" s="33" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="30" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Q6" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="R6" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S6" s="35" t="str">
+        <v>85</v>
+      </c>
+      <c r="R6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S6" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T6" s="35" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T6" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U6" s="35" t="str">
+      <c r="U6" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V6" s="35" t="s">
+        <v>Contêineres</v>
+      </c>
+      <c r="V6" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W6" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-6</v>
+      </c>
+      <c r="X6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA6" s="30" t="str">
+        <f t="shared" si="3"/>
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="59">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C7" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>229</v>
+      </c>
+      <c r="E7" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="F7" s="42" t="s">
         <v>169</v>
       </c>
-      <c r="W6" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-6</v>
-      </c>
-      <c r="X6" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y6" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z6" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA6" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="32">
-        <v>7</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="47" t="s">
-        <v>140</v>
-      </c>
-      <c r="D7" s="47" t="s">
-        <v>230</v>
-      </c>
-      <c r="E7" s="47" t="s">
-        <v>141</v>
-      </c>
-      <c r="F7" s="47" t="s">
-        <v>170</v>
-      </c>
-      <c r="G7" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K7" s="37" t="s">
+      <c r="G7" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L7" s="33" t="str">
@@ -3175,78 +3228,78 @@
         <f t="shared" ref="O7:O45" si="8">IF(ISNUMBER(FIND("Ifc",F7)),CONCATENATE("Classe IFC:   ",F7),CONCATENATE("",F7))</f>
         <v>Sistema.ESG</v>
       </c>
-      <c r="P7" s="58" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q7" s="58" t="s">
-        <v>164</v>
-      </c>
-      <c r="R7" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S7" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T7" s="35" t="s">
+      <c r="P7" s="52" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q7" s="52" t="s">
+        <v>163</v>
+      </c>
+      <c r="R7" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S7" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U7" s="35" t="str">
+      <c r="T7" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U7" s="30" t="str">
         <f t="shared" ref="U7:U37" si="9">SUBSTITUTE(E7, "_", " ")</f>
         <v>Sistema.Sanitário</v>
       </c>
-      <c r="V7" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W7" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-7</v>
+      <c r="V7" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W7" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-7</v>
       </c>
       <c r="X7" s="29" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Y7" s="29" t="s">
-        <v>247</v>
-      </c>
-      <c r="Z7" s="34" t="s">
-        <v>134</v>
+        <v>246</v>
+      </c>
+      <c r="Z7" s="30" t="s">
+        <v>133</v>
       </c>
       <c r="AA7" s="30" t="str">
         <f>_xlfn.TRANSLATE(P7,"pt","en")</f>
         <v>Building Sewer System</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="32">
+    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="59">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="47" t="s">
-        <v>140</v>
-      </c>
-      <c r="D8" s="47" t="s">
-        <v>230</v>
-      </c>
-      <c r="E8" s="47" t="s">
-        <v>142</v>
-      </c>
-      <c r="F8" s="47" t="s">
-        <v>240</v>
-      </c>
-      <c r="G8" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K8" s="37" t="s">
+        <v>275</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="D8" s="42" t="s">
+        <v>229</v>
+      </c>
+      <c r="E8" s="42" t="s">
+        <v>141</v>
+      </c>
+      <c r="F8" s="42" t="s">
+        <v>239</v>
+      </c>
+      <c r="G8" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L8" s="33" t="str">
@@ -3265,78 +3318,78 @@
         <f t="shared" si="8"/>
         <v>Sistema.AFR</v>
       </c>
-      <c r="P8" s="58" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q8" s="58" t="s">
-        <v>162</v>
-      </c>
-      <c r="R8" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S8" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T8" s="35" t="s">
+      <c r="P8" s="52" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q8" s="52" t="s">
+        <v>161</v>
+      </c>
+      <c r="R8" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S8" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U8" s="35" t="str">
+      <c r="T8" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U8" s="30" t="str">
         <f t="shared" ref="U8:U17" si="13">SUBSTITUTE(E8, "_", " ")</f>
         <v>Sistema.Hidráulico</v>
       </c>
-      <c r="V8" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W8" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-8</v>
+      <c r="V8" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W8" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-8</v>
       </c>
       <c r="X8" s="29" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Y8" s="29" t="s">
-        <v>245</v>
-      </c>
-      <c r="Z8" s="34" t="s">
-        <v>171</v>
+        <v>244</v>
+      </c>
+      <c r="Z8" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="AA8" s="30" t="str">
         <f>_xlfn.TRANSLATE(P8,"pt","en")</f>
         <v>Building Cold Water System</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="32">
+    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="59">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="47" t="s">
-        <v>140</v>
-      </c>
-      <c r="D9" s="47" t="s">
-        <v>230</v>
-      </c>
-      <c r="E9" s="47" t="s">
-        <v>142</v>
-      </c>
-      <c r="F9" s="47" t="s">
-        <v>241</v>
-      </c>
-      <c r="G9" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J9" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K9" s="37" t="s">
+        <v>275</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="D9" s="42" t="s">
+        <v>229</v>
+      </c>
+      <c r="E9" s="42" t="s">
+        <v>141</v>
+      </c>
+      <c r="F9" s="42" t="s">
+        <v>240</v>
+      </c>
+      <c r="G9" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L9" s="33" t="str">
@@ -3355,78 +3408,78 @@
         <f t="shared" si="8"/>
         <v>Sistema.AQT</v>
       </c>
-      <c r="P9" s="58" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q9" s="58" t="s">
-        <v>165</v>
-      </c>
-      <c r="R9" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S9" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T9" s="35" t="s">
+      <c r="P9" s="52" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q9" s="52" t="s">
+        <v>164</v>
+      </c>
+      <c r="R9" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S9" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U9" s="35" t="str">
+      <c r="T9" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U9" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Sistema.Hidráulico</v>
       </c>
-      <c r="V9" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W9" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-9</v>
+      <c r="V9" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W9" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-9</v>
       </c>
       <c r="X9" s="29" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Y9" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="Z9" s="34" t="s">
-        <v>171</v>
+        <v>245</v>
+      </c>
+      <c r="Z9" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="AA9" s="30" t="str">
         <f>_xlfn.TRANSLATE(P9,"pt","en")</f>
         <v>Building Hot Water System</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="32">
+    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="59">
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E10" s="47" t="s">
-        <v>239</v>
-      </c>
-      <c r="F10" s="47" t="s">
-        <v>179</v>
-      </c>
-      <c r="G10" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K10" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E10" s="42" t="s">
+        <v>238</v>
+      </c>
+      <c r="F10" s="42" t="s">
+        <v>178</v>
+      </c>
+      <c r="G10" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L10" s="33" t="str">
@@ -3445,78 +3498,78 @@
         <f t="shared" si="8"/>
         <v>Torneira</v>
       </c>
-      <c r="P10" s="58" t="s">
-        <v>179</v>
+      <c r="P10" s="52" t="s">
+        <v>178</v>
       </c>
       <c r="Q10" s="30" t="s">
-        <v>191</v>
-      </c>
-      <c r="R10" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S10" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T10" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="R10" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S10" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U10" s="35" t="str">
+      <c r="T10" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U10" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Peças.Hidráulicas</v>
       </c>
-      <c r="V10" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W10" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-10</v>
+      <c r="V10" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W10" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-10</v>
       </c>
       <c r="X10" s="29" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Y10" s="29" t="s">
-        <v>200</v>
-      </c>
-      <c r="Z10" s="34" t="s">
-        <v>171</v>
+        <v>199</v>
+      </c>
+      <c r="Z10" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="AA10" s="30" t="e" vm="1">
         <f t="shared" ref="AA10:AA17" si="14">_xlfn.TRANSLATE(P10,"pt","en")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="32">
+    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="59">
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E11" s="47" t="s">
-        <v>239</v>
-      </c>
-      <c r="F11" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="G11" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J11" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K11" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>238</v>
+      </c>
+      <c r="F11" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="G11" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J11" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L11" s="33" t="str">
@@ -3535,79 +3588,79 @@
         <f t="shared" si="8"/>
         <v>Misturador</v>
       </c>
-      <c r="P11" s="58" t="s">
-        <v>180</v>
+      <c r="P11" s="52" t="s">
+        <v>179</v>
       </c>
       <c r="Q11" s="30" t="str">
         <f t="shared" ref="Q11:Q17" si="15">_xlfn.TRANSLATE(P11,"pt","es")</f>
         <v>Mezclador</v>
       </c>
-      <c r="R11" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S11" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T11" s="35" t="s">
+      <c r="R11" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S11" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U11" s="35" t="str">
+      <c r="T11" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U11" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Peças.Hidráulicas</v>
       </c>
-      <c r="V11" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W11" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-11</v>
+      <c r="V11" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W11" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-11</v>
       </c>
       <c r="X11" s="29" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Y11" s="29" t="s">
-        <v>200</v>
-      </c>
-      <c r="Z11" s="34" t="s">
-        <v>171</v>
+        <v>199</v>
+      </c>
+      <c r="Z11" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="AA11" s="30" t="str">
         <f t="shared" si="14"/>
         <v>Mixer</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="32">
+    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="59">
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E12" s="47" t="s">
-        <v>239</v>
-      </c>
-      <c r="F12" s="47" t="s">
-        <v>182</v>
-      </c>
-      <c r="G12" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J12" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K12" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E12" s="42" t="s">
+        <v>238</v>
+      </c>
+      <c r="F12" s="42" t="s">
+        <v>181</v>
+      </c>
+      <c r="G12" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K12" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L12" s="33" t="str">
@@ -3626,79 +3679,79 @@
         <f t="shared" si="8"/>
         <v>Registro</v>
       </c>
-      <c r="P12" s="58" t="s">
-        <v>182</v>
+      <c r="P12" s="52" t="s">
+        <v>181</v>
       </c>
       <c r="Q12" s="30" t="str">
         <f t="shared" si="15"/>
         <v>Registro</v>
       </c>
-      <c r="R12" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S12" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T12" s="35" t="s">
+      <c r="R12" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S12" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U12" s="35" t="str">
+      <c r="T12" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U12" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Peças.Hidráulicas</v>
       </c>
-      <c r="V12" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W12" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-12</v>
+      <c r="V12" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W12" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-12</v>
       </c>
       <c r="X12" s="29" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Y12" s="29" t="s">
-        <v>200</v>
-      </c>
-      <c r="Z12" s="34" t="s">
-        <v>171</v>
+        <v>199</v>
+      </c>
+      <c r="Z12" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="AA12" s="30" t="str">
         <f t="shared" si="14"/>
         <v>Registration</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="32">
+    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="59">
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E13" s="47" t="s">
-        <v>239</v>
-      </c>
-      <c r="F13" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="G13" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H13" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I13" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J13" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K13" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E13" s="42" t="s">
+        <v>238</v>
+      </c>
+      <c r="F13" s="42" t="s">
+        <v>180</v>
+      </c>
+      <c r="G13" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K13" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L13" s="33" t="str">
@@ -3717,79 +3770,79 @@
         <f t="shared" si="8"/>
         <v>Válvula</v>
       </c>
-      <c r="P13" s="58" t="s">
-        <v>181</v>
+      <c r="P13" s="52" t="s">
+        <v>180</v>
       </c>
       <c r="Q13" s="30" t="str">
         <f t="shared" si="15"/>
         <v>Válvula</v>
       </c>
-      <c r="R13" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S13" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T13" s="35" t="s">
+      <c r="R13" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S13" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U13" s="35" t="str">
+      <c r="T13" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U13" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Peças.Hidráulicas</v>
       </c>
-      <c r="V13" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W13" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-13</v>
+      <c r="V13" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W13" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-13</v>
       </c>
       <c r="X13" s="29" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Y13" s="29" t="s">
-        <v>200</v>
-      </c>
-      <c r="Z13" s="34" t="s">
-        <v>171</v>
+        <v>199</v>
+      </c>
+      <c r="Z13" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="AA13" s="30" t="str">
         <f t="shared" si="14"/>
         <v>Valve</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="32">
+    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="59">
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E14" s="47" t="s">
-        <v>239</v>
-      </c>
-      <c r="F14" s="47" t="s">
-        <v>178</v>
-      </c>
-      <c r="G14" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H14" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I14" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J14" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K14" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E14" s="42" t="s">
+        <v>238</v>
+      </c>
+      <c r="F14" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="G14" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I14" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J14" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K14" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L14" s="33" t="str">
@@ -3808,79 +3861,79 @@
         <f t="shared" si="8"/>
         <v>Chuveiro</v>
       </c>
-      <c r="P14" s="58" t="s">
-        <v>178</v>
+      <c r="P14" s="52" t="s">
+        <v>177</v>
       </c>
       <c r="Q14" s="30" t="str">
         <f t="shared" si="15"/>
         <v>Ducha</v>
       </c>
-      <c r="R14" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S14" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T14" s="35" t="s">
+      <c r="R14" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S14" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U14" s="35" t="str">
+      <c r="T14" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U14" s="30" t="str">
         <f t="shared" ref="U14:U16" si="19">SUBSTITUTE(E14, "_", " ")</f>
         <v>Peças.Hidráulicas</v>
       </c>
-      <c r="V14" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W14" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-14</v>
+      <c r="V14" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W14" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-14</v>
       </c>
       <c r="X14" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="Y14" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="Y14" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="Z14" s="34" t="s">
-        <v>171</v>
+      <c r="Z14" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="AA14" s="30" t="str">
         <f t="shared" ref="AA14:AA15" si="20">_xlfn.TRANSLATE(P14,"pt","en")</f>
         <v>Shower</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="32">
+    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="59">
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E15" s="47" t="s">
-        <v>239</v>
-      </c>
-      <c r="F15" s="47" t="s">
-        <v>189</v>
-      </c>
-      <c r="G15" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I15" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J15" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K15" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E15" s="42" t="s">
+        <v>238</v>
+      </c>
+      <c r="F15" s="42" t="s">
+        <v>188</v>
+      </c>
+      <c r="G15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K15" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L15" s="33" t="str">
@@ -3899,79 +3952,79 @@
         <f t="shared" si="8"/>
         <v>Ducha</v>
       </c>
-      <c r="P15" s="58" t="s">
-        <v>190</v>
+      <c r="P15" s="52" t="s">
+        <v>189</v>
       </c>
       <c r="Q15" s="30" t="str">
         <f t="shared" ref="Q15" si="21">_xlfn.TRANSLATE(P15,"pt","es")</f>
         <v>Ducha manual</v>
       </c>
-      <c r="R15" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S15" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T15" s="35" t="s">
+      <c r="R15" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S15" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U15" s="35" t="str">
+      <c r="T15" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U15" s="30" t="str">
         <f t="shared" si="19"/>
         <v>Peças.Hidráulicas</v>
       </c>
-      <c r="V15" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W15" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-15</v>
+      <c r="V15" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W15" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-15</v>
       </c>
       <c r="X15" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="Y15" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="Y15" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="Z15" s="34" t="s">
-        <v>171</v>
+      <c r="Z15" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="AA15" s="30" t="str">
         <f t="shared" si="20"/>
         <v>Manual shower</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="32">
+    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="59">
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="E16" s="42" t="s">
+        <v>238</v>
+      </c>
+      <c r="F16" s="42" t="s">
         <v>252</v>
       </c>
-      <c r="E16" s="47" t="s">
-        <v>239</v>
-      </c>
-      <c r="F16" s="47" t="s">
-        <v>253</v>
-      </c>
-      <c r="G16" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H16" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I16" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J16" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K16" s="37" t="s">
+      <c r="G16" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L16" s="33" t="str">
@@ -3990,77 +4043,77 @@
         <f t="shared" si="8"/>
         <v>Medidor.de.Água</v>
       </c>
-      <c r="P16" s="58" t="s">
+      <c r="P16" s="52" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q16" s="52" t="s">
         <v>254</v>
       </c>
-      <c r="Q16" s="58" t="s">
-        <v>255</v>
-      </c>
-      <c r="R16" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S16" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T16" s="35" t="s">
+      <c r="R16" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S16" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U16" s="35" t="str">
+      <c r="T16" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U16" s="30" t="str">
         <f t="shared" si="19"/>
         <v>Peças.Hidráulicas</v>
       </c>
-      <c r="V16" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W16" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-16</v>
+      <c r="V16" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W16" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-16</v>
       </c>
       <c r="X16" s="29" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Y16" s="29" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z16" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="AA16" s="30" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="59">
+        <v>17</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="Z16" s="34" t="s">
-        <v>171</v>
-      </c>
-      <c r="AA16" s="30" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="32">
-        <v>17</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="47" t="s">
-        <v>140</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E17" s="47" t="s">
-        <v>239</v>
-      </c>
-      <c r="F17" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="G17" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H17" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K17" s="37" t="s">
+      <c r="E17" s="42" t="s">
+        <v>238</v>
+      </c>
+      <c r="F17" s="42" t="s">
+        <v>231</v>
+      </c>
+      <c r="G17" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K17" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L17" s="33" t="str">
@@ -4079,79 +4132,79 @@
         <f t="shared" si="8"/>
         <v>Acessório.Hidraúlico</v>
       </c>
-      <c r="P17" s="58" t="s">
-        <v>243</v>
+      <c r="P17" s="52" t="s">
+        <v>242</v>
       </c>
       <c r="Q17" s="30" t="str">
         <f t="shared" si="15"/>
         <v>Accesorios para sistemas de agua como soportes, ganchos, pedestales, etc.</v>
       </c>
-      <c r="R17" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S17" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T17" s="35" t="s">
+      <c r="R17" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S17" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U17" s="35" t="str">
+      <c r="T17" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U17" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Peças.Hidráulicas</v>
       </c>
-      <c r="V17" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W17" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-17</v>
+      <c r="V17" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W17" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-17</v>
       </c>
       <c r="X17" s="29" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Y17" s="29" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z17" s="34" t="s">
-        <v>171</v>
+        <v>256</v>
+      </c>
+      <c r="Z17" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="AA17" s="30" t="str">
         <f t="shared" si="14"/>
         <v>Water system accessory like brackets, hooks, pedestals, etc.</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="32">
+    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="59">
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E18" s="47" t="s">
-        <v>233</v>
-      </c>
-      <c r="F18" s="47" t="s">
-        <v>144</v>
-      </c>
-      <c r="G18" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H18" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I18" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J18" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K18" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E18" s="42" t="s">
+        <v>232</v>
+      </c>
+      <c r="F18" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="G18" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J18" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K18" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L18" s="33" t="str">
@@ -4170,79 +4223,79 @@
         <f t="shared" si="8"/>
         <v>Cisterna.Superior</v>
       </c>
-      <c r="P18" s="58" t="s">
-        <v>150</v>
+      <c r="P18" s="52" t="s">
+        <v>149</v>
       </c>
       <c r="Q18" s="30" t="str">
         <f>_xlfn.TRANSLATE(P18,"pt","es")</f>
         <v>Cisterna Superior</v>
       </c>
-      <c r="R18" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S18" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T18" s="35" t="s">
+      <c r="R18" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S18" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U18" s="35" t="str">
+      <c r="T18" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U18" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Tubulação.Agua.Fria</v>
       </c>
-      <c r="V18" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W18" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-18</v>
+      <c r="V18" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W18" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-18</v>
       </c>
       <c r="X18" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Y18" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="Z18" s="34" t="s">
-        <v>171</v>
+        <v>200</v>
+      </c>
+      <c r="Z18" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="AA18" s="30" t="str">
         <f t="shared" ref="AA18:AA32" si="22">_xlfn.TRANSLATE(P18,"pt","en")</f>
         <v>Upper Cistern</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="32">
+    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="59">
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C19" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E19" s="47" t="s">
-        <v>233</v>
-      </c>
-      <c r="F19" s="47" t="s">
-        <v>250</v>
-      </c>
-      <c r="G19" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I19" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J19" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K19" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E19" s="42" t="s">
+        <v>232</v>
+      </c>
+      <c r="F19" s="42" t="s">
+        <v>249</v>
+      </c>
+      <c r="G19" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J19" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K19" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L19" s="33" t="str">
@@ -4261,79 +4314,79 @@
         <f t="shared" si="8"/>
         <v>Cisterna.Intermediária</v>
       </c>
-      <c r="P19" s="58" t="s">
-        <v>159</v>
+      <c r="P19" s="52" t="s">
+        <v>158</v>
       </c>
       <c r="Q19" s="30" t="str">
         <f t="shared" ref="Q19:Q25" si="23">_xlfn.TRANSLATE(P19,"pt","es")</f>
         <v>Cisterna intermedia</v>
       </c>
-      <c r="R19" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S19" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T19" s="35" t="s">
+      <c r="R19" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S19" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U19" s="35" t="str">
+      <c r="T19" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U19" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Tubulação.Agua.Fria</v>
       </c>
-      <c r="V19" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W19" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-19</v>
+      <c r="V19" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W19" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-19</v>
       </c>
       <c r="X19" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Y19" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="Z19" s="34" t="s">
-        <v>171</v>
+        <v>200</v>
+      </c>
+      <c r="Z19" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="AA19" s="30" t="str">
         <f t="shared" si="22"/>
         <v>Intermediate Cistern</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="32">
+    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="59">
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C20" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E20" s="47" t="s">
-        <v>233</v>
-      </c>
-      <c r="F20" s="47" t="s">
-        <v>145</v>
-      </c>
-      <c r="G20" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H20" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I20" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J20" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K20" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E20" s="42" t="s">
+        <v>232</v>
+      </c>
+      <c r="F20" s="42" t="s">
+        <v>144</v>
+      </c>
+      <c r="G20" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H20" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I20" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J20" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K20" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L20" s="33" t="str">
@@ -4352,79 +4405,79 @@
         <f t="shared" si="8"/>
         <v>Cisterna.Inferior</v>
       </c>
-      <c r="P20" s="58" t="s">
-        <v>151</v>
+      <c r="P20" s="52" t="s">
+        <v>150</v>
       </c>
       <c r="Q20" s="30" t="str">
         <f t="shared" si="23"/>
         <v>Cisterna Inferior</v>
       </c>
-      <c r="R20" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S20" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T20" s="35" t="s">
+      <c r="R20" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S20" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U20" s="35" t="str">
+      <c r="T20" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U20" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Tubulação.Agua.Fria</v>
       </c>
-      <c r="V20" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W20" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-20</v>
+      <c r="V20" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W20" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-20</v>
       </c>
       <c r="X20" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Y20" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="Z20" s="34" t="s">
-        <v>171</v>
+        <v>200</v>
+      </c>
+      <c r="Z20" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="AA20" s="30" t="str">
         <f t="shared" si="22"/>
         <v>Lower Cistern</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="32">
+    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="59">
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C21" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E21" s="47" t="s">
-        <v>233</v>
-      </c>
-      <c r="F21" s="47" t="s">
-        <v>149</v>
-      </c>
-      <c r="G21" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H21" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I21" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J21" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K21" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E21" s="42" t="s">
+        <v>232</v>
+      </c>
+      <c r="F21" s="42" t="s">
+        <v>148</v>
+      </c>
+      <c r="G21" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H21" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I21" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J21" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K21" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L21" s="33" t="str">
@@ -4443,79 +4496,79 @@
         <f t="shared" si="8"/>
         <v>Tubulação.AF</v>
       </c>
-      <c r="P21" s="58" t="s">
-        <v>154</v>
+      <c r="P21" s="52" t="s">
+        <v>153</v>
       </c>
       <c r="Q21" s="30" t="str">
         <f t="shared" si="23"/>
         <v>Tubería de agua fría</v>
       </c>
-      <c r="R21" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S21" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T21" s="35" t="s">
+      <c r="R21" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S21" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U21" s="35" t="str">
+      <c r="T21" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U21" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Tubulação.Agua.Fria</v>
       </c>
-      <c r="V21" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W21" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-21</v>
+      <c r="V21" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W21" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-21</v>
       </c>
       <c r="X21" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Y21" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z21" s="34" t="s">
-        <v>171</v>
+        <v>112</v>
+      </c>
+      <c r="Z21" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="AA21" s="30" t="str">
         <f t="shared" si="22"/>
         <v>Cold Water Pipe</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="32">
+    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="59">
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C22" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E22" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="F22" s="47" t="s">
-        <v>152</v>
-      </c>
-      <c r="G22" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H22" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I22" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J22" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K22" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E22" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="F22" s="42" t="s">
+        <v>151</v>
+      </c>
+      <c r="G22" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H22" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I22" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J22" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K22" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L22" s="33" t="str">
@@ -4534,78 +4587,78 @@
         <f t="shared" si="8"/>
         <v>Aquecedor.de.Agua</v>
       </c>
-      <c r="P22" s="58" t="s">
-        <v>153</v>
+      <c r="P22" s="52" t="s">
+        <v>152</v>
       </c>
       <c r="Q22" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="R22" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S22" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T22" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="R22" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S22" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U22" s="35" t="str">
+      <c r="T22" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U22" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Tubulação.Agua.Quente</v>
       </c>
-      <c r="V22" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W22" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-22</v>
+      <c r="V22" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W22" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-22</v>
       </c>
       <c r="X22" s="29" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Y22" s="29" t="s">
-        <v>202</v>
-      </c>
-      <c r="Z22" s="34" t="s">
-        <v>171</v>
+        <v>201</v>
+      </c>
+      <c r="Z22" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="AA22" s="30" t="str">
         <f t="shared" si="22"/>
         <v>Water heater</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="32">
+    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="59">
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C23" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E23" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="F23" s="47" t="s">
-        <v>146</v>
-      </c>
-      <c r="G23" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H23" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I23" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J23" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K23" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E23" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="F23" s="42" t="s">
+        <v>145</v>
+      </c>
+      <c r="G23" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I23" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J23" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K23" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L23" s="33" t="str">
@@ -4624,78 +4677,78 @@
         <f t="shared" si="8"/>
         <v>Boiler</v>
       </c>
-      <c r="P23" s="58" t="s">
-        <v>146</v>
+      <c r="P23" s="52" t="s">
+        <v>145</v>
       </c>
       <c r="Q23" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="R23" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S23" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T23" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="R23" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S23" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U23" s="35" t="str">
+      <c r="T23" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U23" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Tubulação.Agua.Quente</v>
       </c>
-      <c r="V23" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W23" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-23</v>
+      <c r="V23" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W23" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-23</v>
       </c>
       <c r="X23" s="29" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Y23" s="29" t="s">
-        <v>202</v>
-      </c>
-      <c r="Z23" s="34" t="s">
-        <v>171</v>
+        <v>201</v>
+      </c>
+      <c r="Z23" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="AA23" s="30" t="str">
         <f t="shared" si="22"/>
         <v>Boiler</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="32">
+    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="59">
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C24" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E24" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="F24" s="47" t="s">
-        <v>147</v>
-      </c>
-      <c r="G24" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H24" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I24" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J24" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K24" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E24" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="F24" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="G24" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H24" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I24" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J24" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K24" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L24" s="33" t="str">
@@ -4714,79 +4767,79 @@
         <f t="shared" si="8"/>
         <v>Caldeira</v>
       </c>
-      <c r="P24" s="58" t="s">
-        <v>147</v>
+      <c r="P24" s="52" t="s">
+        <v>146</v>
       </c>
       <c r="Q24" s="30" t="str">
         <f t="shared" si="23"/>
         <v>Caldera</v>
       </c>
-      <c r="R24" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S24" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T24" s="35" t="s">
+      <c r="R24" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S24" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U24" s="35" t="str">
+      <c r="T24" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U24" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Tubulação.Agua.Quente</v>
       </c>
-      <c r="V24" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W24" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-24</v>
+      <c r="V24" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W24" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-24</v>
       </c>
       <c r="X24" s="29" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Y24" s="29" t="s">
-        <v>203</v>
-      </c>
-      <c r="Z24" s="34" t="s">
-        <v>171</v>
+        <v>202</v>
+      </c>
+      <c r="Z24" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="AA24" s="30" t="str">
         <f t="shared" si="22"/>
         <v>Boiler</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="32">
+    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="59">
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C25" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E25" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="F25" s="47" t="s">
-        <v>148</v>
-      </c>
-      <c r="G25" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H25" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I25" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J25" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K25" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="F25" s="42" t="s">
+        <v>147</v>
+      </c>
+      <c r="G25" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I25" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J25" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K25" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L25" s="33" t="str">
@@ -4805,79 +4858,79 @@
         <f t="shared" si="8"/>
         <v>Tubulação.AQ</v>
       </c>
-      <c r="P25" s="58" t="s">
-        <v>155</v>
+      <c r="P25" s="52" t="s">
+        <v>154</v>
       </c>
       <c r="Q25" s="30" t="str">
         <f t="shared" si="23"/>
         <v>Tubería de agua caliente</v>
       </c>
-      <c r="R25" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S25" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T25" s="35" t="s">
+      <c r="R25" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S25" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U25" s="35" t="str">
+      <c r="T25" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U25" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Tubulação.Agua.Quente</v>
       </c>
-      <c r="V25" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W25" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-25</v>
+      <c r="V25" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W25" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-25</v>
       </c>
       <c r="X25" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Y25" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z25" s="34" t="s">
-        <v>171</v>
+        <v>112</v>
+      </c>
+      <c r="Z25" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="AA25" s="30" t="str">
         <f t="shared" si="22"/>
         <v>Hot Water Pipe</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="32">
+    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="59">
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C26" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E26" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="F26" s="47" t="s">
-        <v>143</v>
-      </c>
-      <c r="G26" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H26" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I26" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J26" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K26" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E26" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="F26" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="G26" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I26" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J26" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K26" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L26" s="33" t="str">
@@ -4896,78 +4949,78 @@
         <f t="shared" si="8"/>
         <v>Tubulação.Reuso</v>
       </c>
-      <c r="P26" s="58" t="s">
+      <c r="P26" s="52" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q26" s="52" t="s">
         <v>156</v>
       </c>
-      <c r="Q26" s="58" t="s">
-        <v>157</v>
-      </c>
-      <c r="R26" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S26" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T26" s="35" t="s">
+      <c r="R26" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S26" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U26" s="35" t="str">
+      <c r="T26" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U26" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Tubulação.Agua.Quente</v>
       </c>
-      <c r="V26" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W26" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-26</v>
+      <c r="V26" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W26" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-26</v>
       </c>
       <c r="X26" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Y26" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z26" s="34" t="s">
-        <v>171</v>
+        <v>112</v>
+      </c>
+      <c r="Z26" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="AA26" s="30" t="str">
         <f t="shared" si="22"/>
         <v>Reuse Water Pipe</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="32">
+    <row r="27" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="59">
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C27" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E27" s="47" t="s">
-        <v>235</v>
-      </c>
-      <c r="F27" s="47" t="s">
-        <v>185</v>
-      </c>
-      <c r="G27" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H27" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I27" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J27" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K27" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E27" s="42" t="s">
+        <v>234</v>
+      </c>
+      <c r="F27" s="42" t="s">
+        <v>184</v>
+      </c>
+      <c r="G27" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H27" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I27" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J27" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K27" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L27" s="33" t="str">
@@ -4986,78 +5039,78 @@
         <f t="shared" si="8"/>
         <v>Vaso.Sanitário</v>
       </c>
-      <c r="P27" s="58" t="s">
-        <v>192</v>
+      <c r="P27" s="52" t="s">
+        <v>191</v>
       </c>
       <c r="Q27" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="R27" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S27" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T27" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="R27" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S27" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U27" s="35" t="str">
+      <c r="T27" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U27" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Sanitárias</v>
       </c>
-      <c r="V27" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W27" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-27</v>
+      <c r="V27" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W27" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-27</v>
       </c>
       <c r="X27" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="Y27" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="Y27" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="Z27" s="34" t="s">
-        <v>171</v>
+      <c r="Z27" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="AA27" s="30" t="str">
         <f t="shared" si="22"/>
         <v>Toilet</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="32">
+    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="59">
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C28" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E28" s="47" t="s">
-        <v>235</v>
-      </c>
-      <c r="F28" s="47" t="s">
-        <v>184</v>
-      </c>
-      <c r="G28" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H28" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I28" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J28" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K28" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E28" s="42" t="s">
+        <v>234</v>
+      </c>
+      <c r="F28" s="42" t="s">
+        <v>183</v>
+      </c>
+      <c r="G28" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H28" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I28" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J28" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K28" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L28" s="33" t="str">
@@ -5076,79 +5129,79 @@
         <f t="shared" si="8"/>
         <v>Bidet</v>
       </c>
-      <c r="P28" s="58" t="s">
-        <v>184</v>
+      <c r="P28" s="52" t="s">
+        <v>183</v>
       </c>
       <c r="Q28" s="30" t="str">
         <f t="shared" ref="Q28:Q32" si="24">_xlfn.TRANSLATE(P28,"pt","es")</f>
         <v>Bidé</v>
       </c>
-      <c r="R28" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S28" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T28" s="35" t="s">
+      <c r="R28" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S28" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U28" s="35" t="str">
+      <c r="T28" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U28" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Sanitárias</v>
       </c>
-      <c r="V28" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W28" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-28</v>
+      <c r="V28" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W28" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-28</v>
       </c>
       <c r="X28" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="Y28" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="Y28" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="Z28" s="34" t="s">
-        <v>171</v>
+      <c r="Z28" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="AA28" s="30" t="str">
         <f t="shared" si="22"/>
         <v>Bidet</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="32">
+    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="59">
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C29" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C29" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E29" s="47" t="s">
-        <v>235</v>
-      </c>
-      <c r="F29" s="47" t="s">
-        <v>187</v>
-      </c>
-      <c r="G29" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H29" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I29" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J29" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K29" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E29" s="42" t="s">
+        <v>234</v>
+      </c>
+      <c r="F29" s="42" t="s">
+        <v>186</v>
+      </c>
+      <c r="G29" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H29" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I29" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J29" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K29" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L29" s="33" t="str">
@@ -5167,78 +5220,78 @@
         <f t="shared" si="8"/>
         <v>Pia.Sanitária</v>
       </c>
-      <c r="P29" s="58" t="s">
-        <v>193</v>
+      <c r="P29" s="52" t="s">
+        <v>192</v>
       </c>
       <c r="Q29" s="30" t="s">
-        <v>197</v>
-      </c>
-      <c r="R29" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S29" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T29" s="35" t="s">
+        <v>196</v>
+      </c>
+      <c r="R29" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S29" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U29" s="35" t="str">
+      <c r="T29" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U29" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Sanitárias</v>
       </c>
-      <c r="V29" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W29" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-29</v>
+      <c r="V29" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W29" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-29</v>
       </c>
       <c r="X29" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="Y29" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="Y29" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="Z29" s="34" t="s">
-        <v>171</v>
+      <c r="Z29" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="AA29" s="30" t="str">
         <f t="shared" si="22"/>
         <v>Sanitary Sink</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="32">
+    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="59">
         <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C30" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E30" s="47" t="s">
-        <v>235</v>
-      </c>
-      <c r="F30" s="47" t="s">
-        <v>183</v>
-      </c>
-      <c r="G30" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H30" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I30" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J30" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K30" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E30" s="42" t="s">
+        <v>234</v>
+      </c>
+      <c r="F30" s="42" t="s">
+        <v>182</v>
+      </c>
+      <c r="G30" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I30" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J30" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K30" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L30" s="33" t="str">
@@ -5257,79 +5310,79 @@
         <f t="shared" si="8"/>
         <v>Lavatório</v>
       </c>
-      <c r="P30" s="58" t="s">
-        <v>183</v>
+      <c r="P30" s="52" t="s">
+        <v>182</v>
       </c>
       <c r="Q30" s="30" t="str">
         <f t="shared" si="24"/>
         <v>Lavabo</v>
       </c>
-      <c r="R30" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S30" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T30" s="35" t="s">
+      <c r="R30" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S30" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U30" s="35" t="str">
+      <c r="T30" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U30" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Sanitárias</v>
       </c>
-      <c r="V30" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W30" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-30</v>
+      <c r="V30" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W30" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-30</v>
       </c>
       <c r="X30" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="Y30" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="Y30" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="Z30" s="34" t="s">
-        <v>171</v>
+      <c r="Z30" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="AA30" s="30" t="str">
         <f t="shared" si="22"/>
         <v>Washbasin</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="32">
+    <row r="31" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="59">
         <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C31" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C31" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E31" s="47" t="s">
-        <v>235</v>
-      </c>
-      <c r="F31" s="47" t="s">
-        <v>186</v>
-      </c>
-      <c r="G31" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H31" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I31" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J31" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K31" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E31" s="42" t="s">
+        <v>234</v>
+      </c>
+      <c r="F31" s="42" t="s">
+        <v>185</v>
+      </c>
+      <c r="G31" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H31" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I31" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J31" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K31" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L31" s="33" t="str">
@@ -5348,78 +5401,78 @@
         <f t="shared" si="8"/>
         <v>Cuba.Sanitária</v>
       </c>
-      <c r="P31" s="58" t="s">
-        <v>194</v>
+      <c r="P31" s="52" t="s">
+        <v>193</v>
       </c>
       <c r="Q31" s="30" t="s">
-        <v>196</v>
-      </c>
-      <c r="R31" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S31" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T31" s="35" t="s">
+        <v>195</v>
+      </c>
+      <c r="R31" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S31" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U31" s="35" t="str">
+      <c r="T31" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U31" s="30" t="str">
         <f t="shared" ref="U31" si="28">SUBSTITUTE(E31, "_", " ")</f>
         <v>Peças.Sanitárias</v>
       </c>
-      <c r="V31" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W31" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-31</v>
+      <c r="V31" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W31" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-31</v>
       </c>
       <c r="X31" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="Y31" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="Y31" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="Z31" s="34" t="s">
-        <v>171</v>
+      <c r="Z31" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="AA31" s="30" t="str">
         <f t="shared" ref="AA31" si="29">_xlfn.TRANSLATE(P31,"pt","en")</f>
         <v>Sanitary Bowl</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="32">
+    <row r="32" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="59">
         <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C32" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C32" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E32" s="47" t="s">
-        <v>235</v>
-      </c>
-      <c r="F32" s="47" t="s">
-        <v>188</v>
-      </c>
-      <c r="G32" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H32" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I32" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J32" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K32" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E32" s="42" t="s">
+        <v>234</v>
+      </c>
+      <c r="F32" s="42" t="s">
+        <v>187</v>
+      </c>
+      <c r="G32" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H32" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I32" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J32" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K32" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L32" s="33" t="str">
@@ -5438,79 +5491,79 @@
         <f t="shared" si="8"/>
         <v>Banheira</v>
       </c>
-      <c r="P32" s="58" t="s">
-        <v>188</v>
+      <c r="P32" s="52" t="s">
+        <v>187</v>
       </c>
       <c r="Q32" s="30" t="str">
         <f t="shared" si="24"/>
         <v>Bañera</v>
       </c>
-      <c r="R32" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S32" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T32" s="35" t="s">
+      <c r="R32" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S32" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U32" s="35" t="str">
+      <c r="T32" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U32" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Sanitárias</v>
       </c>
-      <c r="V32" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W32" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-32</v>
+      <c r="V32" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W32" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-32</v>
       </c>
       <c r="X32" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="Y32" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="Y32" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="Z32" s="34" t="s">
-        <v>171</v>
+      <c r="Z32" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="AA32" s="30" t="str">
         <f t="shared" si="22"/>
         <v>Bathtub</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="32">
+    <row r="33" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="59">
         <v>33</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C33" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C33" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E33" s="47" t="s">
-        <v>236</v>
-      </c>
-      <c r="F33" s="47" t="s">
-        <v>115</v>
-      </c>
-      <c r="G33" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H33" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I33" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J33" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K33" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E33" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="F33" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="G33" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H33" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I33" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J33" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K33" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L33" s="33" t="str">
@@ -5529,78 +5582,78 @@
         <f t="shared" si="8"/>
         <v>Ventilação.Esgoto</v>
       </c>
-      <c r="P33" s="58" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q33" s="58" t="s">
+      <c r="P33" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q33" s="52" t="s">
+        <v>165</v>
+      </c>
+      <c r="R33" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S33" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="T33" s="30" t="s">
         <v>166</v>
       </c>
-      <c r="R33" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S33" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T33" s="35" t="s">
-        <v>167</v>
-      </c>
-      <c r="U33" s="35" t="str">
+      <c r="U33" s="30" t="str">
         <f t="shared" ref="U33" si="33">SUBSTITUTE(E33, "_", " ")</f>
         <v>Esgoto.Coletores</v>
       </c>
-      <c r="V33" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W33" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-33</v>
+      <c r="V33" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W33" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-33</v>
       </c>
       <c r="X33" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Y33" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z33" s="34" t="s">
-        <v>134</v>
+        <v>112</v>
+      </c>
+      <c r="Z33" s="30" t="s">
+        <v>133</v>
       </c>
       <c r="AA33" s="30" t="str">
         <f>_xlfn.TRANSLATE(P33,"pt","en")</f>
         <v>Sewer Ventilation</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="32">
+    <row r="34" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="59">
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C34" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C34" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E34" s="47" t="s">
-        <v>236</v>
-      </c>
-      <c r="F34" s="47" t="s">
-        <v>177</v>
-      </c>
-      <c r="G34" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H34" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I34" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J34" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K34" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E34" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="F34" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="G34" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H34" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I34" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J34" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K34" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L34" s="33" t="str">
@@ -5619,78 +5672,78 @@
         <f t="shared" si="8"/>
         <v>Ralo.Seco</v>
       </c>
-      <c r="P34" s="58" t="s">
-        <v>117</v>
+      <c r="P34" s="52" t="s">
+        <v>116</v>
       </c>
       <c r="Q34" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="R34" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S34" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T34" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="R34" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S34" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U34" s="35" t="str">
+      <c r="T34" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U34" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Esgoto.Coletores</v>
       </c>
-      <c r="V34" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W34" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-34</v>
+      <c r="V34" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W34" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-34</v>
       </c>
       <c r="X34" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Y34" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z34" s="34" t="s">
-        <v>134</v>
+        <v>112</v>
+      </c>
+      <c r="Z34" s="30" t="s">
+        <v>133</v>
       </c>
       <c r="AA34" s="30" t="str">
         <f t="shared" ref="AA34:AA44" si="34">_xlfn.TRANSLATE(P34,"pt","en")</f>
         <v>Local Collector as a Dry Drain or Basin Valve</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="32">
+    <row r="35" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="59">
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C35" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C35" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E35" s="47" t="s">
-        <v>236</v>
-      </c>
-      <c r="F35" s="47" t="s">
-        <v>176</v>
-      </c>
-      <c r="G35" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H35" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I35" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J35" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K35" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E35" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="F35" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="G35" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H35" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I35" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J35" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K35" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L35" s="33" t="str">
@@ -5709,78 +5762,78 @@
         <f t="shared" si="8"/>
         <v>Ralo.Sifonado</v>
       </c>
-      <c r="P35" s="58" t="s">
-        <v>116</v>
+      <c r="P35" s="52" t="s">
+        <v>115</v>
       </c>
       <c r="Q35" s="30" t="s">
-        <v>128</v>
-      </c>
-      <c r="R35" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S35" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T35" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="R35" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S35" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U35" s="35" t="str">
+      <c r="T35" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U35" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Esgoto.Coletores</v>
       </c>
-      <c r="V35" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W35" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-35</v>
+      <c r="V35" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W35" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-35</v>
       </c>
       <c r="X35" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Y35" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z35" s="34" t="s">
-        <v>134</v>
+        <v>112</v>
+      </c>
+      <c r="Z35" s="30" t="s">
+        <v>133</v>
       </c>
       <c r="AA35" s="30" t="str">
         <f t="shared" si="34"/>
         <v>Siphoned Collector as a Siphoned Drain</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="32">
+    <row r="36" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="59">
         <v>36</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C36" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C36" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E36" s="47" t="s">
-        <v>236</v>
-      </c>
-      <c r="F36" s="47" t="s">
-        <v>106</v>
-      </c>
-      <c r="G36" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H36" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I36" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J36" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K36" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E36" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="F36" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="G36" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H36" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I36" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J36" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K36" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L36" s="33" t="str">
@@ -5799,78 +5852,78 @@
         <f t="shared" si="8"/>
         <v>Coletor.Andar</v>
       </c>
-      <c r="P36" s="58" t="s">
-        <v>118</v>
+      <c r="P36" s="52" t="s">
+        <v>117</v>
       </c>
       <c r="Q36" s="30" t="s">
-        <v>260</v>
-      </c>
-      <c r="R36" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S36" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T36" s="35" t="s">
+        <v>259</v>
+      </c>
+      <c r="R36" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S36" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U36" s="35" t="str">
+      <c r="T36" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U36" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Esgoto.Coletores</v>
       </c>
-      <c r="V36" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W36" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-36</v>
+      <c r="V36" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W36" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-36</v>
       </c>
       <c r="X36" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Y36" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z36" s="34" t="s">
-        <v>134</v>
+        <v>112</v>
+      </c>
+      <c r="Z36" s="30" t="s">
+        <v>133</v>
       </c>
       <c r="AA36" s="30" t="str">
         <f t="shared" si="34"/>
         <v>Floor Horizontal Collection Branch</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="32">
+    <row r="37" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="59">
         <v>37</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C37" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C37" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E37" s="47" t="s">
-        <v>236</v>
-      </c>
-      <c r="F37" s="47" t="s">
-        <v>105</v>
-      </c>
-      <c r="G37" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H37" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I37" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J37" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K37" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E37" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="F37" s="42" t="s">
+        <v>104</v>
+      </c>
+      <c r="G37" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H37" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I37" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J37" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K37" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L37" s="33" t="str">
@@ -5889,78 +5942,78 @@
         <f t="shared" si="8"/>
         <v>Coletor.Predial</v>
       </c>
-      <c r="P37" s="58" t="s">
-        <v>119</v>
+      <c r="P37" s="52" t="s">
+        <v>118</v>
       </c>
       <c r="Q37" s="30" t="s">
-        <v>261</v>
-      </c>
-      <c r="R37" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S37" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T37" s="35" t="s">
+        <v>260</v>
+      </c>
+      <c r="R37" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S37" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U37" s="35" t="str">
+      <c r="T37" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U37" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Esgoto.Coletores</v>
       </c>
-      <c r="V37" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W37" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-37</v>
+      <c r="V37" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W37" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-37</v>
       </c>
       <c r="X37" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Y37" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z37" s="34" t="s">
-        <v>134</v>
+        <v>112</v>
+      </c>
+      <c r="Z37" s="30" t="s">
+        <v>133</v>
       </c>
       <c r="AA37" s="30" t="str">
         <f t="shared" si="34"/>
         <v>Horizontal collection branch of the building</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="32">
+    <row r="38" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="59">
         <v>38</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C38" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C38" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E38" s="47" t="s">
-        <v>236</v>
-      </c>
-      <c r="F38" s="47" t="s">
-        <v>107</v>
-      </c>
-      <c r="G38" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H38" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I38" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J38" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K38" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E38" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="F38" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="G38" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H38" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I38" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J38" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K38" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L38" s="33" t="str">
@@ -5979,78 +6032,78 @@
         <f t="shared" si="8"/>
         <v>Tubo.de.Queda</v>
       </c>
-      <c r="P38" s="58" t="s">
-        <v>120</v>
+      <c r="P38" s="52" t="s">
+        <v>119</v>
       </c>
       <c r="Q38" s="30" t="s">
-        <v>262</v>
-      </c>
-      <c r="R38" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S38" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T38" s="35" t="s">
+        <v>261</v>
+      </c>
+      <c r="R38" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S38" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U38" s="35" t="str">
+      <c r="T38" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U38" s="30" t="str">
         <f t="shared" ref="U38" si="38">SUBSTITUTE(E38, "_", " ")</f>
         <v>Esgoto.Coletores</v>
       </c>
-      <c r="V38" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W38" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-38</v>
+      <c r="V38" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W38" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-38</v>
       </c>
       <c r="X38" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Y38" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z38" s="34" t="s">
-        <v>134</v>
+        <v>112</v>
+      </c>
+      <c r="Z38" s="30" t="s">
+        <v>133</v>
       </c>
       <c r="AA38" s="30" t="str">
         <f t="shared" si="34"/>
         <v>Downpipe</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="32">
+    <row r="39" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="59">
         <v>39</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C39" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C39" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E39" s="47" t="s">
-        <v>236</v>
-      </c>
-      <c r="F39" s="47" t="s">
-        <v>231</v>
-      </c>
-      <c r="G39" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H39" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I39" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J39" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K39" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E39" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="F39" s="42" t="s">
+        <v>230</v>
+      </c>
+      <c r="G39" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H39" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I39" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J39" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K39" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L39" s="33" t="str">
@@ -6069,78 +6122,78 @@
         <f t="shared" si="8"/>
         <v>Fecho.Hidráulico</v>
       </c>
-      <c r="P39" s="58" t="s">
-        <v>121</v>
+      <c r="P39" s="52" t="s">
+        <v>120</v>
       </c>
       <c r="Q39" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="R39" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S39" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T39" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="R39" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S39" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U39" s="35" t="str">
+      <c r="T39" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U39" s="30" t="str">
         <f t="shared" ref="U39" si="42">SUBSTITUTE(E39, "_", " ")</f>
         <v>Esgoto.Coletores</v>
       </c>
-      <c r="V39" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W39" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-39</v>
+      <c r="V39" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W39" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-39</v>
       </c>
       <c r="X39" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Y39" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z39" s="34" t="s">
-        <v>134</v>
+        <v>112</v>
+      </c>
+      <c r="Z39" s="30" t="s">
+        <v>133</v>
       </c>
       <c r="AA39" s="30" t="str">
         <f t="shared" si="34"/>
         <v>Siphons</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="32">
+    <row r="40" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="59">
         <v>40</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C40" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C40" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E40" s="47" t="s">
-        <v>237</v>
-      </c>
-      <c r="F40" s="47" t="s">
-        <v>111</v>
-      </c>
-      <c r="G40" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H40" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I40" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J40" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K40" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E40" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="F40" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="G40" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H40" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I40" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J40" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K40" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L40" s="33" t="str">
@@ -6159,78 +6212,78 @@
         <f t="shared" si="8"/>
         <v>Caixa.de.Areia</v>
       </c>
-      <c r="P40" s="58" t="s">
-        <v>122</v>
+      <c r="P40" s="52" t="s">
+        <v>121</v>
       </c>
       <c r="Q40" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="R40" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S40" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T40" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="R40" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S40" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U40" s="35" t="str">
+      <c r="T40" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U40" s="30" t="str">
         <f t="shared" ref="U40:U44" si="46">SUBSTITUTE(E40, "_", " ")</f>
         <v>Esgoto.Visitas</v>
       </c>
-      <c r="V40" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W40" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-40</v>
+      <c r="V40" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W40" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-40</v>
       </c>
       <c r="X40" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Y40" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z40" s="34" t="s">
-        <v>134</v>
+        <v>112</v>
+      </c>
+      <c r="Z40" s="30" t="s">
+        <v>133</v>
       </c>
       <c r="AA40" s="30" t="str">
         <f t="shared" si="34"/>
         <v>Sandboxes</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="32">
+    <row r="41" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="59">
         <v>41</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C41" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C41" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E41" s="47" t="s">
-        <v>237</v>
-      </c>
-      <c r="F41" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="G41" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H41" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I41" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J41" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K41" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E41" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="F41" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="G41" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H41" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I41" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J41" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K41" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L41" s="33" t="str">
@@ -6249,78 +6302,78 @@
         <f t="shared" si="8"/>
         <v>Caixa.de.Gordura</v>
       </c>
-      <c r="P41" s="58" t="s">
-        <v>123</v>
+      <c r="P41" s="52" t="s">
+        <v>122</v>
       </c>
       <c r="Q41" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="R41" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S41" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T41" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="R41" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S41" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U41" s="35" t="str">
+      <c r="T41" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U41" s="30" t="str">
         <f t="shared" si="46"/>
         <v>Esgoto.Visitas</v>
       </c>
-      <c r="V41" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W41" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-41</v>
+      <c r="V41" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W41" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-41</v>
       </c>
       <c r="X41" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Y41" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z41" s="34" t="s">
-        <v>134</v>
+        <v>112</v>
+      </c>
+      <c r="Z41" s="30" t="s">
+        <v>133</v>
       </c>
       <c r="AA41" s="30" t="str">
         <f t="shared" si="34"/>
         <v>Grease Traps</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="32">
+    <row r="42" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="59">
         <v>42</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C42" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C42" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E42" s="47" t="s">
-        <v>237</v>
-      </c>
-      <c r="F42" s="47" t="s">
-        <v>108</v>
-      </c>
-      <c r="G42" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H42" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I42" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J42" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K42" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E42" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="F42" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="G42" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H42" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I42" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J42" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K42" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L42" s="33" t="str">
@@ -6339,78 +6392,78 @@
         <f t="shared" si="8"/>
         <v>Caixa.de.Inspeção</v>
       </c>
-      <c r="P42" s="58" t="s">
-        <v>124</v>
+      <c r="P42" s="52" t="s">
+        <v>123</v>
       </c>
       <c r="Q42" s="30" t="s">
-        <v>259</v>
-      </c>
-      <c r="R42" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S42" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T42" s="35" t="s">
+        <v>258</v>
+      </c>
+      <c r="R42" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S42" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U42" s="35" t="str">
+      <c r="T42" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U42" s="30" t="str">
         <f t="shared" ref="U42:U43" si="50">SUBSTITUTE(E42, "_", " ")</f>
         <v>Esgoto.Visitas</v>
       </c>
-      <c r="V42" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W42" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-42</v>
+      <c r="V42" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W42" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-42</v>
       </c>
       <c r="X42" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Y42" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z42" s="34" t="s">
-        <v>134</v>
+        <v>112</v>
+      </c>
+      <c r="Z42" s="30" t="s">
+        <v>133</v>
       </c>
       <c r="AA42" s="30" t="str">
         <f t="shared" si="34"/>
         <v>Manholes</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="32">
+    <row r="43" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="59">
         <v>43</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C43" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C43" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E43" s="47" t="s">
-        <v>237</v>
-      </c>
-      <c r="F43" s="47" t="s">
-        <v>112</v>
-      </c>
-      <c r="G43" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H43" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I43" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J43" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K43" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E43" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="F43" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="G43" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H43" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I43" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J43" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K43" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L43" s="33" t="str">
@@ -6429,78 +6482,78 @@
         <f t="shared" si="8"/>
         <v>Caixa.Sifonada</v>
       </c>
-      <c r="P43" s="58" t="s">
-        <v>125</v>
+      <c r="P43" s="52" t="s">
+        <v>124</v>
       </c>
       <c r="Q43" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="R43" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S43" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T43" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="R43" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S43" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U43" s="35" t="str">
+      <c r="T43" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U43" s="30" t="str">
         <f t="shared" si="50"/>
         <v>Esgoto.Visitas</v>
       </c>
-      <c r="V43" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W43" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-43</v>
+      <c r="V43" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W43" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-43</v>
       </c>
       <c r="X43" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Y43" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z43" s="34" t="s">
-        <v>134</v>
+        <v>112</v>
+      </c>
+      <c r="Z43" s="30" t="s">
+        <v>133</v>
       </c>
       <c r="AA43" s="30" t="str">
         <f t="shared" si="34"/>
         <v>Siphon Boxes</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="32">
+    <row r="44" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="59">
         <v>44</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C44" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C44" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E44" s="47" t="s">
-        <v>237</v>
-      </c>
-      <c r="F44" s="47" t="s">
-        <v>109</v>
-      </c>
-      <c r="G44" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H44" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I44" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J44" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K44" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E44" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="F44" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="G44" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H44" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I44" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J44" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K44" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L44" s="33" t="str">
@@ -6519,78 +6572,78 @@
         <f t="shared" si="8"/>
         <v>Poço.de.Visita</v>
       </c>
-      <c r="P44" s="58" t="s">
-        <v>126</v>
+      <c r="P44" s="52" t="s">
+        <v>125</v>
       </c>
       <c r="Q44" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="R44" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S44" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T44" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="R44" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S44" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U44" s="35" t="str">
+      <c r="T44" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U44" s="30" t="str">
         <f t="shared" si="46"/>
         <v>Esgoto.Visitas</v>
       </c>
-      <c r="V44" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W44" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-44</v>
+      <c r="V44" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W44" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-44</v>
       </c>
       <c r="X44" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Y44" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z44" s="34" t="s">
-        <v>134</v>
+        <v>112</v>
+      </c>
+      <c r="Z44" s="30" t="s">
+        <v>133</v>
       </c>
       <c r="AA44" s="30" t="str">
         <f t="shared" si="34"/>
         <v>Manholes</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="32">
+    <row r="45" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="59">
         <v>45</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C45" s="47" t="s">
-        <v>140</v>
+        <v>275</v>
+      </c>
+      <c r="C45" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E45" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="F45" s="47" t="s">
-        <v>172</v>
-      </c>
-      <c r="G45" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H45" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I45" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J45" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K45" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E45" s="42" t="s">
+        <v>237</v>
+      </c>
+      <c r="F45" s="42" t="s">
+        <v>171</v>
+      </c>
+      <c r="G45" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H45" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I45" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J45" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K45" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L45" s="33" t="str">
@@ -6609,40 +6662,40 @@
         <f t="shared" si="8"/>
         <v>Acessório.Sanitário</v>
       </c>
-      <c r="P45" s="58" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q45" s="58" t="s">
-        <v>173</v>
-      </c>
-      <c r="R45" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S45" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="T45" s="35" t="s">
+      <c r="P45" s="52" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q45" s="52" t="s">
+        <v>172</v>
+      </c>
+      <c r="R45" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S45" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="U45" s="35" t="str">
+      <c r="T45" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="U45" s="30" t="str">
         <f t="shared" ref="U45" si="54">SUBSTITUTE(E45, "_", " ")</f>
         <v>Esgoto.Acessórios</v>
       </c>
-      <c r="V45" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="W45" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-HSA-45</v>
+      <c r="V45" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W45" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-HIDR-45</v>
       </c>
       <c r="X45" s="29" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Y45" s="29" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z45" s="34" t="s">
-        <v>134</v>
+        <v>256</v>
+      </c>
+      <c r="Z45" s="30" t="s">
+        <v>133</v>
       </c>
       <c r="AA45" s="30" t="str">
         <f t="shared" ref="AA45" si="55">_xlfn.TRANSLATE(P45,"pt","en")</f>
@@ -6654,71 +6707,76 @@
     <sortCondition ref="F7:F936"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:A45">
-    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="30" priority="1487"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="29" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="1494"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="25" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16">
-    <cfRule type="duplicateValues" dxfId="24" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35">
-    <cfRule type="duplicateValues" dxfId="23" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F38 F40:F1048576 F17:F33 F1 F7:F15">
-    <cfRule type="duplicateValues" dxfId="22" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F46:F1048576">
-    <cfRule type="duplicateValues" dxfId="21" priority="244"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="246"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="1459"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="1480"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="251"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="253"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="1466"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="1487"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:O1 A1:D1 Q1:X1">
-    <cfRule type="cellIs" dxfId="17" priority="51" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="58" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P7:P9">
-    <cfRule type="duplicateValues" dxfId="16" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P10:P15 P17:P26">
-    <cfRule type="duplicateValues" dxfId="15" priority="1500"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="1507"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P27:P32">
-    <cfRule type="duplicateValues" dxfId="14" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P33">
-    <cfRule type="duplicateValues" dxfId="13" priority="1493"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="1500"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q7:Q9">
-    <cfRule type="duplicateValues" dxfId="12" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q26">
-    <cfRule type="duplicateValues" dxfId="11" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q33">
-    <cfRule type="duplicateValues" dxfId="10" priority="1494"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1501"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1:AA1">
-    <cfRule type="cellIs" dxfId="9" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="23" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA45">
-    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
+  <conditionalFormatting sqref="AA7:AA45">
+    <cfRule type="cellIs" dxfId="15" priority="13" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:B45">
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F6">
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2:AA6">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6730,15 +6788,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="9"/>
+    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -6803,7 +6861,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -6868,7 +6926,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -6935,7 +6993,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6951,1154 +7009,1154 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S19"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.85" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.23046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.53515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.23046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.53515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.07421875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="56.3828125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.07421875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.07421875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.84375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.23046875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.15234375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.15234375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.921875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.765625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="3.921875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.15234375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.765625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.23046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="77.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="D1" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="E1" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="E1" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="F1" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="G1" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="H1" s="54" t="s">
-        <v>77</v>
-      </c>
       <c r="I1" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J1" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K1" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M1" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N1" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O1" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P1" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q1" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R1" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="S1" s="19" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="20">
         <v>1</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="C2" s="59" t="s">
-        <v>267</v>
-      </c>
-      <c r="D2" s="56" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="57" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="51" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="H2" s="55" t="s">
+        <v>138</v>
+      </c>
+      <c r="H2" s="49" t="s">
         <v>9</v>
       </c>
       <c r="I2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="55" t="s">
+      <c r="J2" s="49" t="s">
         <v>9</v>
       </c>
       <c r="K2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="55" t="s">
+      <c r="L2" s="49" t="s">
         <v>9</v>
       </c>
       <c r="M2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="55" t="s">
+      <c r="N2" s="49" t="s">
         <v>9</v>
       </c>
       <c r="O2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="55" t="s">
+      <c r="P2" s="49" t="s">
         <v>9</v>
       </c>
       <c r="Q2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="R2" s="55" t="s">
+      <c r="R2" s="49" t="s">
         <v>9</v>
       </c>
       <c r="S2" s="24" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20">
         <v>2</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="C3" s="47" t="s">
-        <v>170</v>
-      </c>
-      <c r="D3" s="56" t="s">
-        <v>83</v>
-      </c>
-      <c r="E3" s="38" t="s">
-        <v>100</v>
+        <v>227</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>169</v>
+      </c>
+      <c r="D3" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>99</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>208</v>
-      </c>
-      <c r="H3" s="55" t="s">
-        <v>78</v>
+        <v>207</v>
+      </c>
+      <c r="H3" s="49" t="s">
+        <v>77</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="J3" s="55" t="s">
+        <v>137</v>
+      </c>
+      <c r="J3" s="49" t="s">
         <v>9</v>
       </c>
       <c r="K3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="55" t="s">
+      <c r="L3" s="49" t="s">
         <v>9</v>
       </c>
       <c r="M3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="55" t="s">
+      <c r="N3" s="49" t="s">
         <v>9</v>
       </c>
       <c r="O3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="55" t="s">
+      <c r="P3" s="49" t="s">
         <v>9</v>
       </c>
       <c r="Q3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="R3" s="55" t="s">
+      <c r="R3" s="49" t="s">
         <v>9</v>
       </c>
       <c r="S3" s="24" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20">
         <v>3</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>229</v>
-      </c>
-      <c r="C4" s="47" t="s">
-        <v>240</v>
-      </c>
-      <c r="D4" s="56" t="s">
-        <v>83</v>
-      </c>
-      <c r="E4" s="38" t="s">
-        <v>100</v>
+        <v>228</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>239</v>
+      </c>
+      <c r="D4" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>99</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>209</v>
-      </c>
-      <c r="H4" s="55" t="s">
-        <v>78</v>
+        <v>208</v>
+      </c>
+      <c r="H4" s="49" t="s">
+        <v>77</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="J4" s="55" t="s">
+        <v>137</v>
+      </c>
+      <c r="J4" s="49" t="s">
         <v>9</v>
       </c>
       <c r="K4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="55" t="s">
+      <c r="L4" s="49" t="s">
         <v>9</v>
       </c>
       <c r="M4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="55" t="s">
+      <c r="N4" s="49" t="s">
         <v>9</v>
       </c>
       <c r="O4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="P4" s="55" t="s">
+      <c r="P4" s="49" t="s">
         <v>9</v>
       </c>
       <c r="Q4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="R4" s="55" t="s">
+      <c r="R4" s="49" t="s">
         <v>9</v>
       </c>
       <c r="S4" s="24" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="20">
         <v>4</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>242</v>
-      </c>
-      <c r="C5" s="47" t="s">
         <v>241</v>
       </c>
-      <c r="D5" s="56" t="s">
-        <v>83</v>
-      </c>
-      <c r="E5" s="38" t="s">
-        <v>100</v>
+      <c r="C5" s="42" t="s">
+        <v>240</v>
+      </c>
+      <c r="D5" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>99</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>209</v>
-      </c>
-      <c r="H5" s="55" t="s">
-        <v>78</v>
+        <v>208</v>
+      </c>
+      <c r="H5" s="49" t="s">
+        <v>77</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="J5" s="55" t="s">
+        <v>137</v>
+      </c>
+      <c r="J5" s="49" t="s">
         <v>9</v>
       </c>
       <c r="K5" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="55" t="s">
+      <c r="L5" s="49" t="s">
         <v>9</v>
       </c>
       <c r="M5" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="N5" s="55" t="s">
+      <c r="N5" s="49" t="s">
         <v>9</v>
       </c>
       <c r="O5" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="P5" s="55" t="s">
+      <c r="P5" s="49" t="s">
         <v>9</v>
       </c>
       <c r="Q5" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="R5" s="55" t="s">
+      <c r="R5" s="49" t="s">
         <v>9</v>
       </c>
       <c r="S5" s="24" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="20">
         <v>5</v>
       </c>
-      <c r="B6" s="53" t="s">
-        <v>210</v>
-      </c>
-      <c r="C6" s="47" t="s">
-        <v>176</v>
-      </c>
-      <c r="D6" s="56" t="s">
-        <v>137</v>
-      </c>
-      <c r="E6" s="38" t="s">
-        <v>228</v>
+      <c r="B6" s="47" t="s">
+        <v>209</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>227</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>174</v>
-      </c>
-      <c r="H6" s="55" t="s">
+        <v>173</v>
+      </c>
+      <c r="H6" s="49" t="s">
         <v>9</v>
       </c>
       <c r="I6" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J6" s="55" t="s">
-        <v>277</v>
+      <c r="J6" s="49" t="s">
+        <v>273</v>
       </c>
       <c r="K6" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="L6" s="49" t="s">
+        <v>274</v>
+      </c>
+      <c r="M6" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N6" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O6" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="L6" s="55" t="s">
-        <v>278</v>
-      </c>
-      <c r="M6" s="24" t="s">
+      <c r="P6" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="N6" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O6" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="P6" s="55" t="s">
+      <c r="Q6" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="R6" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q6" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="R6" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S6" s="24" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20">
         <v>6</v>
       </c>
-      <c r="B7" s="53" t="s">
-        <v>211</v>
-      </c>
-      <c r="C7" s="47" t="s">
-        <v>176</v>
-      </c>
-      <c r="D7" s="56" t="s">
-        <v>137</v>
-      </c>
-      <c r="E7" s="38" t="s">
-        <v>228</v>
+      <c r="B7" s="47" t="s">
+        <v>210</v>
+      </c>
+      <c r="C7" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="D7" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>227</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>174</v>
-      </c>
-      <c r="H7" s="55" t="s">
+        <v>173</v>
+      </c>
+      <c r="H7" s="49" t="s">
         <v>9</v>
       </c>
       <c r="I7" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J7" s="55" t="s">
-        <v>277</v>
+      <c r="J7" s="49" t="s">
+        <v>273</v>
       </c>
       <c r="K7" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="L7" s="49" t="s">
+        <v>274</v>
+      </c>
+      <c r="M7" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N7" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O7" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="L7" s="55" t="s">
-        <v>278</v>
-      </c>
-      <c r="M7" s="24" t="s">
+      <c r="P7" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="N7" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O7" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="P7" s="55" t="s">
+      <c r="Q7" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="R7" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q7" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="R7" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S7" s="24" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="20">
         <v>7</v>
       </c>
-      <c r="B8" s="53" t="s">
-        <v>212</v>
-      </c>
-      <c r="C8" s="47" t="s">
-        <v>233</v>
-      </c>
-      <c r="D8" s="56" t="s">
-        <v>137</v>
-      </c>
-      <c r="E8" s="38" t="s">
-        <v>229</v>
+      <c r="B8" s="47" t="s">
+        <v>211</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>232</v>
+      </c>
+      <c r="D8" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>228</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="H8" s="55" t="s">
+        <v>174</v>
+      </c>
+      <c r="H8" s="49" t="s">
         <v>9</v>
       </c>
       <c r="I8" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J8" s="55" t="s">
-        <v>277</v>
+      <c r="J8" s="49" t="s">
+        <v>273</v>
       </c>
       <c r="K8" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="L8" s="55" t="s">
-        <v>278</v>
+        <v>134</v>
+      </c>
+      <c r="L8" s="49" t="s">
+        <v>274</v>
       </c>
       <c r="M8" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N8" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O8" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="P8" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="N8" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O8" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="P8" s="55" t="s">
+      <c r="Q8" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="R8" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q8" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="R8" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S8" s="24" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="20">
         <v>8</v>
       </c>
-      <c r="B9" s="53" t="s">
+      <c r="B9" s="47" t="s">
+        <v>212</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>232</v>
+      </c>
+      <c r="D9" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>228</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="H9" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="49" t="s">
+        <v>273</v>
+      </c>
+      <c r="K9" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="L9" s="49" t="s">
+        <v>274</v>
+      </c>
+      <c r="M9" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N9" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O9" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="P9" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q9" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="R9" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="S9" s="24" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="20">
+        <v>9</v>
+      </c>
+      <c r="B10" s="47" t="s">
         <v>213</v>
       </c>
-      <c r="C9" s="47" t="s">
-        <v>233</v>
-      </c>
-      <c r="D9" s="56" t="s">
-        <v>137</v>
-      </c>
-      <c r="E9" s="38" t="s">
-        <v>229</v>
-      </c>
-      <c r="F9" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="H9" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J9" s="55" t="s">
-        <v>277</v>
-      </c>
-      <c r="K9" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="L9" s="55" t="s">
-        <v>278</v>
-      </c>
-      <c r="M9" s="24" t="s">
+      <c r="C10" s="42" t="s">
+        <v>232</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>228</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="H10" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="49" t="s">
+        <v>273</v>
+      </c>
+      <c r="K10" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="L10" s="49" t="s">
+        <v>274</v>
+      </c>
+      <c r="M10" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N10" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O10" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="P10" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="N9" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O9" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="P9" s="55" t="s">
+      <c r="Q10" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="R10" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q9" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="R9" s="55" t="s">
-        <v>104</v>
-      </c>
-      <c r="S9" s="24" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="20">
-        <v>9</v>
-      </c>
-      <c r="B10" s="53" t="s">
-        <v>214</v>
-      </c>
-      <c r="C10" s="47" t="s">
-        <v>233</v>
-      </c>
-      <c r="D10" s="56" t="s">
-        <v>137</v>
-      </c>
-      <c r="E10" s="38" t="s">
-        <v>229</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="G10" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="H10" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="55" t="s">
-        <v>277</v>
-      </c>
-      <c r="K10" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="L10" s="55" t="s">
-        <v>278</v>
-      </c>
-      <c r="M10" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="N10" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O10" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="P10" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q10" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="R10" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S10" s="24" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="20">
         <v>10</v>
       </c>
-      <c r="B11" s="53" t="s">
-        <v>215</v>
-      </c>
-      <c r="C11" s="47" t="s">
-        <v>233</v>
-      </c>
-      <c r="D11" s="56" t="s">
-        <v>137</v>
-      </c>
-      <c r="E11" s="38" t="s">
-        <v>229</v>
+      <c r="B11" s="47" t="s">
+        <v>214</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>232</v>
+      </c>
+      <c r="D11" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>228</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="H11" s="55" t="s">
+        <v>174</v>
+      </c>
+      <c r="H11" s="49" t="s">
         <v>9</v>
       </c>
       <c r="I11" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J11" s="55" t="s">
-        <v>277</v>
+      <c r="J11" s="49" t="s">
+        <v>273</v>
       </c>
       <c r="K11" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="L11" s="55" t="s">
-        <v>278</v>
+        <v>134</v>
+      </c>
+      <c r="L11" s="49" t="s">
+        <v>274</v>
       </c>
       <c r="M11" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N11" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O11" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="P11" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="N11" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O11" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="P11" s="55" t="s">
+      <c r="Q11" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="R11" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q11" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="R11" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S11" s="24" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="20">
         <v>11</v>
       </c>
-      <c r="B12" s="53" t="s">
-        <v>216</v>
-      </c>
-      <c r="C12" s="47" t="s">
-        <v>233</v>
-      </c>
-      <c r="D12" s="56" t="s">
-        <v>137</v>
-      </c>
-      <c r="E12" s="38" t="s">
-        <v>229</v>
+      <c r="B12" s="47" t="s">
+        <v>215</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>232</v>
+      </c>
+      <c r="D12" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>228</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="H12" s="55" t="s">
+        <v>174</v>
+      </c>
+      <c r="H12" s="49" t="s">
         <v>9</v>
       </c>
       <c r="I12" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J12" s="55" t="s">
-        <v>277</v>
+      <c r="J12" s="49" t="s">
+        <v>273</v>
       </c>
       <c r="K12" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="L12" s="55" t="s">
-        <v>278</v>
+        <v>134</v>
+      </c>
+      <c r="L12" s="49" t="s">
+        <v>274</v>
       </c>
       <c r="M12" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N12" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O12" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="P12" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="N12" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O12" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="P12" s="55" t="s">
+      <c r="Q12" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="R12" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q12" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="R12" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S12" s="24" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="20">
         <v>12</v>
       </c>
-      <c r="B13" s="53" t="s">
-        <v>217</v>
-      </c>
-      <c r="C13" s="47" t="s">
-        <v>233</v>
-      </c>
-      <c r="D13" s="56" t="s">
-        <v>137</v>
-      </c>
-      <c r="E13" s="38" t="s">
-        <v>229</v>
+      <c r="B13" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>232</v>
+      </c>
+      <c r="D13" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>228</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="H13" s="55" t="s">
+        <v>174</v>
+      </c>
+      <c r="H13" s="49" t="s">
         <v>9</v>
       </c>
       <c r="I13" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J13" s="55" t="s">
-        <v>277</v>
+      <c r="J13" s="49" t="s">
+        <v>273</v>
       </c>
       <c r="K13" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="L13" s="55" t="s">
-        <v>278</v>
+        <v>134</v>
+      </c>
+      <c r="L13" s="49" t="s">
+        <v>274</v>
       </c>
       <c r="M13" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N13" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O13" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="P13" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="N13" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O13" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="P13" s="55" t="s">
+      <c r="Q13" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="R13" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q13" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="R13" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S13" s="24" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="20">
         <v>13</v>
       </c>
-      <c r="B14" s="53" t="s">
-        <v>218</v>
-      </c>
-      <c r="C14" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="D14" s="56" t="s">
-        <v>137</v>
-      </c>
-      <c r="E14" s="38" t="s">
-        <v>242</v>
+      <c r="B14" s="47" t="s">
+        <v>217</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="D14" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>241</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G14" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="H14" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="I14" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J14" s="49" t="s">
+        <v>273</v>
+      </c>
+      <c r="K14" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="L14" s="49" t="s">
+        <v>274</v>
+      </c>
+      <c r="M14" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N14" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O14" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="P14" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q14" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="H14" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="I14" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J14" s="55" t="s">
-        <v>277</v>
-      </c>
-      <c r="K14" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="L14" s="55" t="s">
-        <v>278</v>
-      </c>
-      <c r="M14" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="N14" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O14" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="P14" s="55" t="s">
+      <c r="R14" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q14" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="R14" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S14" s="24" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="20">
         <v>14</v>
       </c>
-      <c r="B15" s="53" t="s">
-        <v>219</v>
-      </c>
-      <c r="C15" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="D15" s="56" t="s">
-        <v>137</v>
-      </c>
-      <c r="E15" s="38" t="s">
-        <v>242</v>
+      <c r="B15" s="47" t="s">
+        <v>218</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="D15" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>241</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G15" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="H15" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J15" s="49" t="s">
+        <v>273</v>
+      </c>
+      <c r="K15" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="L15" s="49" t="s">
+        <v>274</v>
+      </c>
+      <c r="M15" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N15" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O15" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="P15" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q15" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="H15" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="I15" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J15" s="55" t="s">
-        <v>277</v>
-      </c>
-      <c r="K15" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="L15" s="55" t="s">
-        <v>278</v>
-      </c>
-      <c r="M15" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="N15" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O15" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="P15" s="55" t="s">
+      <c r="R15" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q15" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="R15" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S15" s="24" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="20">
         <v>15</v>
       </c>
-      <c r="B16" s="53" t="s">
-        <v>220</v>
-      </c>
-      <c r="C16" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="D16" s="56" t="s">
-        <v>137</v>
-      </c>
-      <c r="E16" s="38" t="s">
-        <v>242</v>
+      <c r="B16" s="47" t="s">
+        <v>219</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="D16" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>241</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G16" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="H16" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="49" t="s">
+        <v>273</v>
+      </c>
+      <c r="K16" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="L16" s="49" t="s">
+        <v>274</v>
+      </c>
+      <c r="M16" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N16" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O16" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="P16" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q16" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="H16" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="I16" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J16" s="55" t="s">
-        <v>277</v>
-      </c>
-      <c r="K16" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="L16" s="55" t="s">
-        <v>278</v>
-      </c>
-      <c r="M16" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="N16" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O16" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="P16" s="55" t="s">
+      <c r="R16" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q16" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="R16" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S16" s="24" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="20">
         <v>16</v>
       </c>
-      <c r="B17" s="53" t="s">
-        <v>221</v>
-      </c>
-      <c r="C17" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="D17" s="56" t="s">
-        <v>137</v>
-      </c>
-      <c r="E17" s="38" t="s">
-        <v>242</v>
+      <c r="B17" s="47" t="s">
+        <v>220</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="D17" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>241</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G17" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="H17" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="49" t="s">
+        <v>273</v>
+      </c>
+      <c r="K17" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="L17" s="49" t="s">
+        <v>274</v>
+      </c>
+      <c r="M17" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N17" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O17" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="P17" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q17" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="H17" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17" s="55" t="s">
-        <v>277</v>
-      </c>
-      <c r="K17" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="L17" s="55" t="s">
-        <v>278</v>
-      </c>
-      <c r="M17" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="N17" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O17" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="P17" s="55" t="s">
+      <c r="R17" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q17" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="R17" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S17" s="24" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="20">
         <v>17</v>
       </c>
-      <c r="B18" s="53" t="s">
-        <v>222</v>
-      </c>
-      <c r="C18" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="D18" s="56" t="s">
-        <v>137</v>
-      </c>
-      <c r="E18" s="38" t="s">
-        <v>242</v>
+      <c r="B18" s="47" t="s">
+        <v>221</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="D18" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="E18" s="34" t="s">
+        <v>241</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G18" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="H18" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J18" s="49" t="s">
+        <v>273</v>
+      </c>
+      <c r="K18" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="L18" s="49" t="s">
+        <v>274</v>
+      </c>
+      <c r="M18" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N18" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O18" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="P18" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q18" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="H18" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="I18" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J18" s="55" t="s">
-        <v>277</v>
-      </c>
-      <c r="K18" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="L18" s="55" t="s">
-        <v>278</v>
-      </c>
-      <c r="M18" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="N18" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O18" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="P18" s="55" t="s">
+      <c r="R18" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q18" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="R18" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S18" s="24" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20">
         <v>18</v>
       </c>
-      <c r="B19" s="53" t="s">
-        <v>223</v>
-      </c>
-      <c r="C19" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="D19" s="56" t="s">
-        <v>137</v>
-      </c>
-      <c r="E19" s="38" t="s">
-        <v>242</v>
+      <c r="B19" s="47" t="s">
+        <v>222</v>
+      </c>
+      <c r="C19" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="D19" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="E19" s="34" t="s">
+        <v>241</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G19" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="H19" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J19" s="49" t="s">
+        <v>273</v>
+      </c>
+      <c r="K19" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="L19" s="49" t="s">
+        <v>274</v>
+      </c>
+      <c r="M19" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N19" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O19" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="P19" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q19" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="H19" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="I19" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J19" s="55" t="s">
-        <v>277</v>
-      </c>
-      <c r="K19" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="L19" s="55" t="s">
-        <v>278</v>
-      </c>
-      <c r="M19" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="N19" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O19" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="P19" s="55" t="s">
+      <c r="R19" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q19" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="R19" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S19" s="24" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3:C5">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8108,38 +8166,38 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.07421875" style="26" customWidth="1"/>
-    <col min="2" max="2" width="5.921875" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.23046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.140625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.85546875" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="31">
         <v>0</v>
       </c>
       <c r="B1" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="D1" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="28" t="s">
-        <v>82</v>
-      </c>
       <c r="E1" s="28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G1" s="28" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -8168,22 +8226,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/HIDS/Ontologia_HidroSanitaria.xlsx
+++ b/Versão5/HIDS/Ontologia_HidroSanitaria.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\HIDS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56016967-CD35-4586-AD00-F73F19195B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4C1A202-BEA3-41D2-88FB-CBF5D57FEB56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -513,9 +513,6 @@
     <t>"Indivíduo Conteiner Superior que representa Informações contidas no Projeto Específico 01"</t>
   </si>
   <si>
-    <t>Sistema.Predial</t>
-  </si>
-  <si>
     <t>Sistema.Sanitário</t>
   </si>
   <si>
@@ -783,9 +780,6 @@
     <t>Sis_AFR_01</t>
   </si>
   <si>
-    <t>Sistema.HidroSanitário</t>
-  </si>
-  <si>
     <t>Fecho.Hidráulico</t>
   </si>
   <si>
@@ -849,9 +843,6 @@
     <t>[ IfcFlowMeter ]</t>
   </si>
   <si>
-    <t>Elementos.Hidráulica</t>
-  </si>
-  <si>
     <t>Medidor.de.Água</t>
   </si>
   <si>
@@ -921,13 +912,22 @@
     <t>quem.forneceu</t>
   </si>
   <si>
-    <t>Conceito</t>
-  </si>
-  <si>
     <t>Contêineres</t>
   </si>
   <si>
     <t>[ 5I ]</t>
+  </si>
+  <si>
+    <t>Conceitos</t>
+  </si>
+  <si>
+    <t>Sistemas.Prediais</t>
+  </si>
+  <si>
+    <t>Elementos.Hidráulicos</t>
+  </si>
+  <si>
+    <t>Sistemas.Hidrossanitários</t>
   </si>
 </sst>
 </file>
@@ -1460,71 +1460,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="39">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="32">
     <dxf>
       <font>
         <b val="0"/>
@@ -2322,15 +2258,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="56" customWidth="1"/>
-    <col min="2" max="2" width="40.140625" style="56" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="56"/>
+    <col min="1" max="1" width="8.69140625" style="56" customWidth="1"/>
+    <col min="2" max="2" width="40.15234375" style="56" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="56"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>44</v>
       </c>
@@ -2341,7 +2277,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
         <v>46</v>
       </c>
@@ -2352,18 +2288,18 @@
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="13" t="s">
         <v>48</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C3" s="40" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>49</v>
       </c>
@@ -2374,7 +2310,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>50</v>
       </c>
@@ -2386,7 +2322,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>51</v>
       </c>
@@ -2398,7 +2334,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -2409,7 +2345,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="37" t="s">
         <v>54</v>
       </c>
@@ -2420,7 +2356,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>55</v>
       </c>
@@ -2431,7 +2367,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>57</v>
       </c>
@@ -2442,7 +2378,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>59</v>
       </c>
@@ -2453,7 +2389,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>60</v>
       </c>
@@ -2464,7 +2400,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>61</v>
       </c>
@@ -2475,7 +2411,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>62</v>
       </c>
@@ -2486,7 +2422,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>63</v>
       </c>
@@ -2497,7 +2433,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>64</v>
       </c>
@@ -2508,30 +2444,30 @@
         <v>93</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>65</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C17" s="40" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46216.386411574073</v>
+        <v>46243.523182175923</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
         <v>67</v>
       </c>
@@ -2542,7 +2478,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="14" t="s">
         <v>69</v>
       </c>
@@ -2553,7 +2489,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>70</v>
       </c>
@@ -2564,29 +2500,29 @@
         <v>93</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>71</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C22" s="40" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>72</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C23" s="40" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14" t="s">
         <v>91</v>
       </c>
@@ -2607,35 +2543,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA45"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" style="54" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" style="54" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" style="62" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.84375" style="54" customWidth="1"/>
+    <col min="4" max="4" width="12.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.3046875" style="54" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.15234375" style="62" bestFit="1" customWidth="1"/>
     <col min="7" max="11" width="8" style="54" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.85546875" style="54" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.28515625" style="54" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="64.5703125" style="54" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.84375" style="54" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.3046875" style="54" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.15234375" style="54" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="64.53515625" style="54" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="41" style="54" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.85546875" style="54" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.85546875" style="54" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.28515625" style="54" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.5703125" style="54" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="43.85546875" style="54" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="19.28515625" style="55" customWidth="1"/>
-    <col min="26" max="26" width="7.28515625" style="54" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="67.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="54"/>
+    <col min="18" max="18" width="3.84375" style="54" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.84375" style="54" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.3046875" style="54" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.53515625" style="54" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="43.84375" style="54" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="19.3046875" style="55" customWidth="1"/>
+    <col min="26" max="26" width="7.3046875" style="54" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="67.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.15234375" style="54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="43" t="s">
         <v>96</v>
       </c>
@@ -2718,21 +2654,21 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="59">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>84</v>
       </c>
       <c r="E2" s="58" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F2" s="58" t="s">
         <v>83</v>
@@ -2769,7 +2705,7 @@
         <v>Contêiner</v>
       </c>
       <c r="P2" s="30" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="Q2" s="30" t="s">
         <v>85</v>
@@ -2790,7 +2726,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V2" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W2" s="60" t="str">
         <f>CONCATENATE("Key-HIDR-",A2)</f>
@@ -2803,31 +2739,31 @@
         <v>9</v>
       </c>
       <c r="Z2" s="30" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="AA2" s="30" t="str">
         <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="59">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>84</v>
       </c>
       <c r="E3" s="58" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F3" s="58" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="G3" s="61" t="s">
         <v>9</v>
@@ -2861,7 +2797,7 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>85</v>
@@ -2882,7 +2818,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V3" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W3" s="60" t="str">
         <f t="shared" ref="W3:W45" si="4">CONCATENATE("Key-HIDR-",A3)</f>
@@ -2902,24 +2838,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="59">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>84</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="G4" s="61" t="s">
         <v>9</v>
@@ -2953,7 +2889,7 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="30" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="Q4" s="30" t="s">
         <v>85</v>
@@ -2974,7 +2910,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V4" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W4" s="60" t="str">
         <f t="shared" si="4"/>
@@ -2994,24 +2930,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="59">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>84</v>
       </c>
       <c r="E5" s="58" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F5" s="58" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G5" s="61" t="s">
         <v>9</v>
@@ -3045,7 +2981,7 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="30" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="Q5" s="30" t="s">
         <v>85</v>
@@ -3066,7 +3002,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V5" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W5" s="60" t="str">
         <f t="shared" si="4"/>
@@ -3086,24 +3022,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="59">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>84</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F6" s="58" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G6" s="61" t="s">
         <v>9</v>
@@ -3137,7 +3073,7 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="30" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Q6" s="30" t="s">
         <v>85</v>
@@ -3158,7 +3094,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V6" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W6" s="60" t="str">
         <f t="shared" si="4"/>
@@ -3178,24 +3114,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="59">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C7" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="D7" s="42" t="s">
+        <v>277</v>
+      </c>
+      <c r="E7" s="42" t="s">
         <v>139</v>
       </c>
-      <c r="D7" s="42" t="s">
-        <v>229</v>
-      </c>
-      <c r="E7" s="42" t="s">
-        <v>140</v>
-      </c>
       <c r="F7" s="42" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G7" s="61" t="s">
         <v>9</v>
@@ -3214,11 +3150,11 @@
       </c>
       <c r="L7" s="33" t="str">
         <f t="shared" ref="L7:L37" si="5">CONCATENATE("", C7)</f>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M7" s="33" t="str">
         <f t="shared" ref="M7:M37" si="6">CONCATENATE("", D7)</f>
-        <v>Sistema.HidroSanitário</v>
+        <v>Sistemas.Hidrossanitários</v>
       </c>
       <c r="N7" s="33" t="str">
         <f t="shared" ref="N7:N37" si="7">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E7),"."," ")," De "," de "))</f>
@@ -3229,36 +3165,36 @@
         <v>Sistema.ESG</v>
       </c>
       <c r="P7" s="52" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q7" s="52" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R7" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S7" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T7" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U7" s="30" t="str">
         <f t="shared" ref="U7:U37" si="9">SUBSTITUTE(E7, "_", " ")</f>
         <v>Sistema.Sanitário</v>
       </c>
       <c r="V7" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W7" s="60" t="str">
         <f t="shared" si="4"/>
         <v>Key-HIDR-7</v>
       </c>
       <c r="X7" s="29" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Y7" s="29" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="Z7" s="30" t="s">
         <v>133</v>
@@ -3268,24 +3204,24 @@
         <v>Building Sewer System</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="59">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C8" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C8" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D8" s="42" t="s">
-        <v>229</v>
+        <v>277</v>
       </c>
       <c r="E8" s="42" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F8" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G8" s="61" t="s">
         <v>9</v>
@@ -3304,11 +3240,11 @@
       </c>
       <c r="L8" s="33" t="str">
         <f t="shared" ref="L8:L17" si="10">CONCATENATE("", C8)</f>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M8" s="33" t="str">
         <f t="shared" ref="M8:M17" si="11">CONCATENATE("", D8)</f>
-        <v>Sistema.HidroSanitário</v>
+        <v>Sistemas.Hidrossanitários</v>
       </c>
       <c r="N8" s="33" t="str">
         <f t="shared" ref="N8:N17" si="12">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E8),"."," ")," De "," de "))</f>
@@ -3319,63 +3255,63 @@
         <v>Sistema.AFR</v>
       </c>
       <c r="P8" s="52" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q8" s="52" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="R8" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S8" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T8" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U8" s="30" t="str">
         <f t="shared" ref="U8:U17" si="13">SUBSTITUTE(E8, "_", " ")</f>
         <v>Sistema.Hidráulico</v>
       </c>
       <c r="V8" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W8" s="60" t="str">
         <f t="shared" si="4"/>
         <v>Key-HIDR-8</v>
       </c>
       <c r="X8" s="29" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Y8" s="29" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="Z8" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA8" s="30" t="str">
         <f>_xlfn.TRANSLATE(P8,"pt","en")</f>
         <v>Building Cold Water System</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="59">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C9" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C9" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D9" s="42" t="s">
-        <v>229</v>
+        <v>277</v>
       </c>
       <c r="E9" s="42" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F9" s="42" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G9" s="61" t="s">
         <v>9</v>
@@ -3394,11 +3330,11 @@
       </c>
       <c r="L9" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M9" s="33" t="str">
         <f t="shared" si="11"/>
-        <v>Sistema.HidroSanitário</v>
+        <v>Sistemas.Hidrossanitários</v>
       </c>
       <c r="N9" s="33" t="str">
         <f t="shared" si="12"/>
@@ -3409,63 +3345,63 @@
         <v>Sistema.AQT</v>
       </c>
       <c r="P9" s="52" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q9" s="52" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R9" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S9" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T9" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U9" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Sistema.Hidráulico</v>
       </c>
       <c r="V9" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W9" s="60" t="str">
         <f t="shared" si="4"/>
         <v>Key-HIDR-9</v>
       </c>
       <c r="X9" s="29" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Y9" s="29" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Z9" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA9" s="30" t="str">
         <f>_xlfn.TRANSLATE(P9,"pt","en")</f>
         <v>Building Hot Water System</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="59">
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C10" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C10" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D10" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E10" s="42" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F10" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G10" s="61" t="s">
         <v>9</v>
@@ -3484,11 +3420,11 @@
       </c>
       <c r="L10" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M10" s="33" t="str">
         <f t="shared" si="11"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N10" s="33" t="str">
         <f t="shared" si="12"/>
@@ -3499,63 +3435,63 @@
         <v>Torneira</v>
       </c>
       <c r="P10" s="52" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q10" s="30" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R10" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S10" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T10" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U10" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Peças.Hidráulicas</v>
       </c>
       <c r="V10" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W10" s="60" t="str">
         <f t="shared" si="4"/>
         <v>Key-HIDR-10</v>
       </c>
       <c r="X10" s="29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Y10" s="29" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Z10" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA10" s="30" t="e" vm="1">
         <f t="shared" ref="AA10:AA17" si="14">_xlfn.TRANSLATE(P10,"pt","en")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="59">
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C11" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C11" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D11" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E11" s="42" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F11" s="42" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G11" s="61" t="s">
         <v>9</v>
@@ -3574,11 +3510,11 @@
       </c>
       <c r="L11" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M11" s="33" t="str">
         <f t="shared" si="11"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N11" s="33" t="str">
         <f t="shared" si="12"/>
@@ -3589,7 +3525,7 @@
         <v>Misturador</v>
       </c>
       <c r="P11" s="52" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q11" s="30" t="str">
         <f t="shared" ref="Q11:Q17" si="15">_xlfn.TRANSLATE(P11,"pt","es")</f>
@@ -3599,54 +3535,54 @@
         <v>9</v>
       </c>
       <c r="S11" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T11" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U11" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Peças.Hidráulicas</v>
       </c>
       <c r="V11" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W11" s="60" t="str">
         <f t="shared" si="4"/>
         <v>Key-HIDR-11</v>
       </c>
       <c r="X11" s="29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Y11" s="29" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Z11" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA11" s="30" t="str">
         <f t="shared" si="14"/>
         <v>Mixer</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="59">
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C12" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C12" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D12" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E12" s="42" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F12" s="42" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G12" s="61" t="s">
         <v>9</v>
@@ -3665,11 +3601,11 @@
       </c>
       <c r="L12" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M12" s="33" t="str">
         <f t="shared" si="11"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N12" s="33" t="str">
         <f t="shared" si="12"/>
@@ -3680,7 +3616,7 @@
         <v>Registro</v>
       </c>
       <c r="P12" s="52" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q12" s="30" t="str">
         <f t="shared" si="15"/>
@@ -3690,54 +3626,54 @@
         <v>9</v>
       </c>
       <c r="S12" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T12" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U12" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Peças.Hidráulicas</v>
       </c>
       <c r="V12" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W12" s="60" t="str">
         <f t="shared" si="4"/>
         <v>Key-HIDR-12</v>
       </c>
       <c r="X12" s="29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Y12" s="29" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Z12" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA12" s="30" t="str">
         <f t="shared" si="14"/>
         <v>Registration</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="59">
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C13" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C13" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D13" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E13" s="42" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F13" s="42" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G13" s="61" t="s">
         <v>9</v>
@@ -3756,11 +3692,11 @@
       </c>
       <c r="L13" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M13" s="33" t="str">
         <f t="shared" si="11"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N13" s="33" t="str">
         <f t="shared" si="12"/>
@@ -3771,7 +3707,7 @@
         <v>Válvula</v>
       </c>
       <c r="P13" s="52" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q13" s="30" t="str">
         <f t="shared" si="15"/>
@@ -3781,54 +3717,54 @@
         <v>9</v>
       </c>
       <c r="S13" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T13" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U13" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Peças.Hidráulicas</v>
       </c>
       <c r="V13" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W13" s="60" t="str">
         <f t="shared" si="4"/>
         <v>Key-HIDR-13</v>
       </c>
       <c r="X13" s="29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Y13" s="29" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Z13" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA13" s="30" t="str">
         <f t="shared" si="14"/>
         <v>Valve</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="59">
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C14" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C14" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D14" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E14" s="42" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F14" s="42" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G14" s="61" t="s">
         <v>9</v>
@@ -3847,11 +3783,11 @@
       </c>
       <c r="L14" s="33" t="str">
         <f t="shared" ref="L14:L16" si="16">CONCATENATE("", C14)</f>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M14" s="33" t="str">
         <f t="shared" ref="M14:M16" si="17">CONCATENATE("", D14)</f>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N14" s="33" t="str">
         <f t="shared" ref="N14:N16" si="18">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E14),"."," ")," De "," de "))</f>
@@ -3862,7 +3798,7 @@
         <v>Chuveiro</v>
       </c>
       <c r="P14" s="52" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q14" s="30" t="str">
         <f t="shared" si="15"/>
@@ -3872,54 +3808,54 @@
         <v>9</v>
       </c>
       <c r="S14" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T14" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U14" s="30" t="str">
         <f t="shared" ref="U14:U16" si="19">SUBSTITUTE(E14, "_", " ")</f>
         <v>Peças.Hidráulicas</v>
       </c>
       <c r="V14" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W14" s="60" t="str">
         <f t="shared" si="4"/>
         <v>Key-HIDR-14</v>
       </c>
       <c r="X14" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y14" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="Y14" s="29" t="s">
-        <v>198</v>
-      </c>
       <c r="Z14" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA14" s="30" t="str">
         <f t="shared" ref="AA14:AA15" si="20">_xlfn.TRANSLATE(P14,"pt","en")</f>
         <v>Shower</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="59">
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C15" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C15" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D15" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E15" s="42" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F15" s="42" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G15" s="61" t="s">
         <v>9</v>
@@ -3938,11 +3874,11 @@
       </c>
       <c r="L15" s="33" t="str">
         <f t="shared" si="16"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M15" s="33" t="str">
         <f t="shared" si="17"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N15" s="33" t="str">
         <f t="shared" si="18"/>
@@ -3953,7 +3889,7 @@
         <v>Ducha</v>
       </c>
       <c r="P15" s="52" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q15" s="30" t="str">
         <f t="shared" ref="Q15" si="21">_xlfn.TRANSLATE(P15,"pt","es")</f>
@@ -3963,54 +3899,54 @@
         <v>9</v>
       </c>
       <c r="S15" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T15" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U15" s="30" t="str">
         <f t="shared" si="19"/>
         <v>Peças.Hidráulicas</v>
       </c>
       <c r="V15" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W15" s="60" t="str">
         <f t="shared" si="4"/>
         <v>Key-HIDR-15</v>
       </c>
       <c r="X15" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y15" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="Y15" s="29" t="s">
-        <v>198</v>
-      </c>
       <c r="Z15" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA15" s="30" t="str">
         <f t="shared" si="20"/>
         <v>Manual shower</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="59">
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C16" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C16" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D16" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E16" s="42" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F16" s="42" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="G16" s="61" t="s">
         <v>9</v>
@@ -4029,11 +3965,11 @@
       </c>
       <c r="L16" s="33" t="str">
         <f t="shared" si="16"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M16" s="33" t="str">
         <f t="shared" si="17"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N16" s="33" t="str">
         <f t="shared" si="18"/>
@@ -4044,62 +3980,62 @@
         <v>Medidor.de.Água</v>
       </c>
       <c r="P16" s="52" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="Q16" s="52" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="R16" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S16" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T16" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U16" s="30" t="str">
         <f t="shared" si="19"/>
         <v>Peças.Hidráulicas</v>
       </c>
       <c r="V16" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W16" s="60" t="str">
         <f t="shared" si="4"/>
         <v>Key-HIDR-16</v>
       </c>
       <c r="X16" s="29" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="Y16" s="29" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="Z16" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA16" s="30" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="59">
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C17" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C17" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D17" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E17" s="42" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F17" s="42" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G17" s="61" t="s">
         <v>9</v>
@@ -4118,11 +4054,11 @@
       </c>
       <c r="L17" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M17" s="33" t="str">
         <f t="shared" si="11"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N17" s="33" t="str">
         <f t="shared" si="12"/>
@@ -4133,7 +4069,7 @@
         <v>Acessório.Hidraúlico</v>
       </c>
       <c r="P17" s="52" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="Q17" s="30" t="str">
         <f t="shared" si="15"/>
@@ -4143,54 +4079,54 @@
         <v>9</v>
       </c>
       <c r="S17" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T17" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U17" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Peças.Hidráulicas</v>
       </c>
       <c r="V17" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W17" s="60" t="str">
         <f t="shared" si="4"/>
         <v>Key-HIDR-17</v>
       </c>
       <c r="X17" s="29" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="Y17" s="29" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="Z17" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA17" s="30" t="str">
         <f t="shared" si="14"/>
         <v>Water system accessory like brackets, hooks, pedestals, etc.</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="59">
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C18" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C18" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D18" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E18" s="42" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F18" s="42" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G18" s="61" t="s">
         <v>9</v>
@@ -4209,11 +4145,11 @@
       </c>
       <c r="L18" s="33" t="str">
         <f t="shared" si="5"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M18" s="33" t="str">
         <f t="shared" si="6"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N18" s="33" t="str">
         <f t="shared" si="7"/>
@@ -4224,7 +4160,7 @@
         <v>Cisterna.Superior</v>
       </c>
       <c r="P18" s="52" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Q18" s="30" t="str">
         <f>_xlfn.TRANSLATE(P18,"pt","es")</f>
@@ -4234,17 +4170,17 @@
         <v>9</v>
       </c>
       <c r="S18" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T18" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U18" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Tubulação.Agua.Fria</v>
       </c>
       <c r="V18" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W18" s="60" t="str">
         <f t="shared" si="4"/>
@@ -4254,34 +4190,34 @@
         <v>113</v>
       </c>
       <c r="Y18" s="29" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Z18" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA18" s="30" t="str">
         <f t="shared" ref="AA18:AA32" si="22">_xlfn.TRANSLATE(P18,"pt","en")</f>
         <v>Upper Cistern</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="59">
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C19" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C19" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D19" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E19" s="42" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F19" s="42" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G19" s="61" t="s">
         <v>9</v>
@@ -4300,11 +4236,11 @@
       </c>
       <c r="L19" s="33" t="str">
         <f t="shared" si="5"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M19" s="33" t="str">
         <f t="shared" si="6"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N19" s="33" t="str">
         <f t="shared" si="7"/>
@@ -4315,7 +4251,7 @@
         <v>Cisterna.Intermediária</v>
       </c>
       <c r="P19" s="52" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q19" s="30" t="str">
         <f t="shared" ref="Q19:Q25" si="23">_xlfn.TRANSLATE(P19,"pt","es")</f>
@@ -4325,17 +4261,17 @@
         <v>9</v>
       </c>
       <c r="S19" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T19" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U19" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Tubulação.Agua.Fria</v>
       </c>
       <c r="V19" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W19" s="60" t="str">
         <f t="shared" si="4"/>
@@ -4345,34 +4281,34 @@
         <v>113</v>
       </c>
       <c r="Y19" s="29" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Z19" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA19" s="30" t="str">
         <f t="shared" si="22"/>
         <v>Intermediate Cistern</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="59">
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C20" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C20" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D20" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E20" s="42" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F20" s="42" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G20" s="61" t="s">
         <v>9</v>
@@ -4391,11 +4327,11 @@
       </c>
       <c r="L20" s="33" t="str">
         <f t="shared" si="5"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M20" s="33" t="str">
         <f t="shared" si="6"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N20" s="33" t="str">
         <f t="shared" si="7"/>
@@ -4406,7 +4342,7 @@
         <v>Cisterna.Inferior</v>
       </c>
       <c r="P20" s="52" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q20" s="30" t="str">
         <f t="shared" si="23"/>
@@ -4416,17 +4352,17 @@
         <v>9</v>
       </c>
       <c r="S20" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T20" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U20" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Tubulação.Agua.Fria</v>
       </c>
       <c r="V20" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W20" s="60" t="str">
         <f t="shared" si="4"/>
@@ -4436,34 +4372,34 @@
         <v>113</v>
       </c>
       <c r="Y20" s="29" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Z20" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA20" s="30" t="str">
         <f t="shared" si="22"/>
         <v>Lower Cistern</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="59">
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C21" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C21" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D21" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E21" s="42" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F21" s="42" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G21" s="61" t="s">
         <v>9</v>
@@ -4482,11 +4418,11 @@
       </c>
       <c r="L21" s="33" t="str">
         <f t="shared" si="5"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M21" s="33" t="str">
         <f t="shared" si="6"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N21" s="33" t="str">
         <f t="shared" si="7"/>
@@ -4497,7 +4433,7 @@
         <v>Tubulação.AF</v>
       </c>
       <c r="P21" s="52" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q21" s="30" t="str">
         <f t="shared" si="23"/>
@@ -4507,17 +4443,17 @@
         <v>9</v>
       </c>
       <c r="S21" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T21" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U21" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Tubulação.Agua.Fria</v>
       </c>
       <c r="V21" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W21" s="60" t="str">
         <f t="shared" si="4"/>
@@ -4530,31 +4466,31 @@
         <v>112</v>
       </c>
       <c r="Z21" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA21" s="30" t="str">
         <f t="shared" si="22"/>
         <v>Cold Water Pipe</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="59">
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C22" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C22" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D22" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E22" s="42" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F22" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G22" s="61" t="s">
         <v>9</v>
@@ -4573,11 +4509,11 @@
       </c>
       <c r="L22" s="33" t="str">
         <f t="shared" si="5"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M22" s="33" t="str">
         <f t="shared" si="6"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N22" s="33" t="str">
         <f t="shared" si="7"/>
@@ -4588,63 +4524,63 @@
         <v>Aquecedor.de.Agua</v>
       </c>
       <c r="P22" s="52" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q22" s="30" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R22" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S22" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T22" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U22" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Tubulação.Agua.Quente</v>
       </c>
       <c r="V22" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W22" s="60" t="str">
         <f t="shared" si="4"/>
         <v>Key-HIDR-22</v>
       </c>
       <c r="X22" s="29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Y22" s="29" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Z22" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA22" s="30" t="str">
         <f t="shared" si="22"/>
         <v>Water heater</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="59">
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C23" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C23" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D23" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E23" s="42" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F23" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G23" s="61" t="s">
         <v>9</v>
@@ -4663,11 +4599,11 @@
       </c>
       <c r="L23" s="33" t="str">
         <f t="shared" si="5"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M23" s="33" t="str">
         <f t="shared" si="6"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N23" s="33" t="str">
         <f t="shared" si="7"/>
@@ -4678,63 +4614,63 @@
         <v>Boiler</v>
       </c>
       <c r="P23" s="52" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q23" s="30" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="R23" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S23" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T23" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U23" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Tubulação.Agua.Quente</v>
       </c>
       <c r="V23" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W23" s="60" t="str">
         <f t="shared" si="4"/>
         <v>Key-HIDR-23</v>
       </c>
       <c r="X23" s="29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Y23" s="29" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Z23" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA23" s="30" t="str">
         <f t="shared" si="22"/>
         <v>Boiler</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="59">
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C24" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C24" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D24" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E24" s="42" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F24" s="42" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G24" s="61" t="s">
         <v>9</v>
@@ -4753,11 +4689,11 @@
       </c>
       <c r="L24" s="33" t="str">
         <f t="shared" si="5"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M24" s="33" t="str">
         <f t="shared" si="6"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N24" s="33" t="str">
         <f t="shared" si="7"/>
@@ -4768,7 +4704,7 @@
         <v>Caldeira</v>
       </c>
       <c r="P24" s="52" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q24" s="30" t="str">
         <f t="shared" si="23"/>
@@ -4778,54 +4714,54 @@
         <v>9</v>
       </c>
       <c r="S24" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T24" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U24" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Tubulação.Agua.Quente</v>
       </c>
       <c r="V24" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W24" s="60" t="str">
         <f t="shared" si="4"/>
         <v>Key-HIDR-24</v>
       </c>
       <c r="X24" s="29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Y24" s="29" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Z24" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA24" s="30" t="str">
         <f t="shared" si="22"/>
         <v>Boiler</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="59">
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C25" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C25" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D25" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E25" s="42" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F25" s="42" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G25" s="61" t="s">
         <v>9</v>
@@ -4844,11 +4780,11 @@
       </c>
       <c r="L25" s="33" t="str">
         <f t="shared" si="5"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M25" s="33" t="str">
         <f t="shared" si="6"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N25" s="33" t="str">
         <f t="shared" si="7"/>
@@ -4859,7 +4795,7 @@
         <v>Tubulação.AQ</v>
       </c>
       <c r="P25" s="52" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q25" s="30" t="str">
         <f t="shared" si="23"/>
@@ -4869,17 +4805,17 @@
         <v>9</v>
       </c>
       <c r="S25" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T25" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U25" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Tubulação.Agua.Quente</v>
       </c>
       <c r="V25" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W25" s="60" t="str">
         <f t="shared" si="4"/>
@@ -4892,31 +4828,31 @@
         <v>112</v>
       </c>
       <c r="Z25" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA25" s="30" t="str">
         <f t="shared" si="22"/>
         <v>Hot Water Pipe</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="59">
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C26" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C26" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D26" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E26" s="42" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F26" s="42" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G26" s="61" t="s">
         <v>9</v>
@@ -4935,11 +4871,11 @@
       </c>
       <c r="L26" s="33" t="str">
         <f t="shared" si="5"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M26" s="33" t="str">
         <f t="shared" si="6"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N26" s="33" t="str">
         <f t="shared" si="7"/>
@@ -4950,26 +4886,26 @@
         <v>Tubulação.Reuso</v>
       </c>
       <c r="P26" s="52" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q26" s="52" t="s">
         <v>155</v>
       </c>
-      <c r="Q26" s="52" t="s">
-        <v>156</v>
-      </c>
       <c r="R26" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S26" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T26" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U26" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Tubulação.Agua.Quente</v>
       </c>
       <c r="V26" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W26" s="60" t="str">
         <f t="shared" si="4"/>
@@ -4982,31 +4918,31 @@
         <v>112</v>
       </c>
       <c r="Z26" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA26" s="30" t="str">
         <f t="shared" si="22"/>
         <v>Reuse Water Pipe</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="59">
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C27" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C27" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D27" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E27" s="42" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F27" s="42" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G27" s="61" t="s">
         <v>9</v>
@@ -5025,11 +4961,11 @@
       </c>
       <c r="L27" s="33" t="str">
         <f t="shared" si="5"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M27" s="33" t="str">
         <f t="shared" si="6"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N27" s="33" t="str">
         <f t="shared" si="7"/>
@@ -5040,63 +4976,63 @@
         <v>Vaso.Sanitário</v>
       </c>
       <c r="P27" s="52" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q27" s="30" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R27" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S27" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T27" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U27" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Sanitárias</v>
       </c>
       <c r="V27" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W27" s="60" t="str">
         <f t="shared" si="4"/>
         <v>Key-HIDR-27</v>
       </c>
       <c r="X27" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y27" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="Y27" s="29" t="s">
-        <v>198</v>
-      </c>
       <c r="Z27" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA27" s="30" t="str">
         <f t="shared" si="22"/>
         <v>Toilet</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="59">
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C28" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C28" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D28" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E28" s="42" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F28" s="42" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G28" s="61" t="s">
         <v>9</v>
@@ -5115,11 +5051,11 @@
       </c>
       <c r="L28" s="33" t="str">
         <f t="shared" si="5"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M28" s="33" t="str">
         <f t="shared" si="6"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N28" s="33" t="str">
         <f t="shared" si="7"/>
@@ -5130,7 +5066,7 @@
         <v>Bidet</v>
       </c>
       <c r="P28" s="52" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q28" s="30" t="str">
         <f t="shared" ref="Q28:Q32" si="24">_xlfn.TRANSLATE(P28,"pt","es")</f>
@@ -5140,54 +5076,54 @@
         <v>9</v>
       </c>
       <c r="S28" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T28" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U28" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Sanitárias</v>
       </c>
       <c r="V28" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W28" s="60" t="str">
         <f t="shared" si="4"/>
         <v>Key-HIDR-28</v>
       </c>
       <c r="X28" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y28" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="Y28" s="29" t="s">
-        <v>198</v>
-      </c>
       <c r="Z28" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA28" s="30" t="str">
         <f t="shared" si="22"/>
         <v>Bidet</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="59">
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C29" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C29" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D29" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E29" s="42" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F29" s="42" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G29" s="61" t="s">
         <v>9</v>
@@ -5206,11 +5142,11 @@
       </c>
       <c r="L29" s="33" t="str">
         <f t="shared" si="5"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M29" s="33" t="str">
         <f t="shared" si="6"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N29" s="33" t="str">
         <f t="shared" si="7"/>
@@ -5221,63 +5157,63 @@
         <v>Pia.Sanitária</v>
       </c>
       <c r="P29" s="52" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q29" s="30" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="R29" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S29" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T29" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U29" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Sanitárias</v>
       </c>
       <c r="V29" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W29" s="60" t="str">
         <f t="shared" si="4"/>
         <v>Key-HIDR-29</v>
       </c>
       <c r="X29" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y29" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="Y29" s="29" t="s">
-        <v>198</v>
-      </c>
       <c r="Z29" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA29" s="30" t="str">
         <f t="shared" si="22"/>
         <v>Sanitary Sink</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="59">
         <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C30" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C30" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D30" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E30" s="42" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F30" s="42" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G30" s="61" t="s">
         <v>9</v>
@@ -5296,11 +5232,11 @@
       </c>
       <c r="L30" s="33" t="str">
         <f t="shared" si="5"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M30" s="33" t="str">
         <f t="shared" si="6"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N30" s="33" t="str">
         <f t="shared" si="7"/>
@@ -5311,7 +5247,7 @@
         <v>Lavatório</v>
       </c>
       <c r="P30" s="52" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q30" s="30" t="str">
         <f t="shared" si="24"/>
@@ -5321,54 +5257,54 @@
         <v>9</v>
       </c>
       <c r="S30" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T30" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U30" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Sanitárias</v>
       </c>
       <c r="V30" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W30" s="60" t="str">
         <f t="shared" si="4"/>
         <v>Key-HIDR-30</v>
       </c>
       <c r="X30" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y30" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="Y30" s="29" t="s">
-        <v>198</v>
-      </c>
       <c r="Z30" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA30" s="30" t="str">
         <f t="shared" si="22"/>
         <v>Washbasin</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="59">
         <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C31" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C31" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D31" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E31" s="42" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F31" s="42" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G31" s="61" t="s">
         <v>9</v>
@@ -5387,11 +5323,11 @@
       </c>
       <c r="L31" s="33" t="str">
         <f t="shared" ref="L31" si="25">CONCATENATE("", C31)</f>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M31" s="33" t="str">
         <f t="shared" ref="M31" si="26">CONCATENATE("", D31)</f>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N31" s="33" t="str">
         <f t="shared" ref="N31" si="27">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E31),"."," ")," De "," de "))</f>
@@ -5402,63 +5338,63 @@
         <v>Cuba.Sanitária</v>
       </c>
       <c r="P31" s="52" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q31" s="30" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R31" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S31" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T31" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U31" s="30" t="str">
         <f t="shared" ref="U31" si="28">SUBSTITUTE(E31, "_", " ")</f>
         <v>Peças.Sanitárias</v>
       </c>
       <c r="V31" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W31" s="60" t="str">
         <f t="shared" si="4"/>
         <v>Key-HIDR-31</v>
       </c>
       <c r="X31" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y31" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="Y31" s="29" t="s">
-        <v>198</v>
-      </c>
       <c r="Z31" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA31" s="30" t="str">
         <f t="shared" ref="AA31" si="29">_xlfn.TRANSLATE(P31,"pt","en")</f>
         <v>Sanitary Bowl</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="59">
         <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C32" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C32" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D32" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E32" s="42" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F32" s="42" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G32" s="61" t="s">
         <v>9</v>
@@ -5477,11 +5413,11 @@
       </c>
       <c r="L32" s="33" t="str">
         <f t="shared" si="5"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M32" s="33" t="str">
         <f t="shared" si="6"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N32" s="33" t="str">
         <f t="shared" si="7"/>
@@ -5492,7 +5428,7 @@
         <v>Banheira</v>
       </c>
       <c r="P32" s="52" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q32" s="30" t="str">
         <f t="shared" si="24"/>
@@ -5502,51 +5438,51 @@
         <v>9</v>
       </c>
       <c r="S32" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T32" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U32" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Sanitárias</v>
       </c>
       <c r="V32" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W32" s="60" t="str">
         <f t="shared" si="4"/>
         <v>Key-HIDR-32</v>
       </c>
       <c r="X32" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y32" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="Y32" s="29" t="s">
-        <v>198</v>
-      </c>
       <c r="Z32" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA32" s="30" t="str">
         <f t="shared" si="22"/>
         <v>Bathtub</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="59">
         <v>33</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C33" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C33" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D33" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E33" s="42" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F33" s="42" t="s">
         <v>114</v>
@@ -5568,11 +5504,11 @@
       </c>
       <c r="L33" s="33" t="str">
         <f t="shared" ref="L33" si="30">CONCATENATE("", C33)</f>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M33" s="33" t="str">
         <f t="shared" ref="M33" si="31">CONCATENATE("", D33)</f>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N33" s="33" t="str">
         <f t="shared" ref="N33" si="32">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E33),"."," ")," De "," de "))</f>
@@ -5583,26 +5519,26 @@
         <v>Ventilação.Esgoto</v>
       </c>
       <c r="P33" s="52" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q33" s="52" t="s">
+        <v>164</v>
+      </c>
+      <c r="R33" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S33" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="T33" s="30" t="s">
         <v>165</v>
-      </c>
-      <c r="R33" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S33" s="30" t="s">
-        <v>167</v>
-      </c>
-      <c r="T33" s="30" t="s">
-        <v>166</v>
       </c>
       <c r="U33" s="30" t="str">
         <f t="shared" ref="U33" si="33">SUBSTITUTE(E33, "_", " ")</f>
         <v>Esgoto.Coletores</v>
       </c>
       <c r="V33" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W33" s="60" t="str">
         <f t="shared" si="4"/>
@@ -5622,24 +5558,24 @@
         <v>Sewer Ventilation</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="59">
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C34" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C34" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D34" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E34" s="42" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F34" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G34" s="61" t="s">
         <v>9</v>
@@ -5658,11 +5594,11 @@
       </c>
       <c r="L34" s="33" t="str">
         <f t="shared" si="5"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M34" s="33" t="str">
         <f t="shared" si="6"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N34" s="33" t="str">
         <f t="shared" si="7"/>
@@ -5682,17 +5618,17 @@
         <v>9</v>
       </c>
       <c r="S34" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T34" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U34" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Esgoto.Coletores</v>
       </c>
       <c r="V34" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W34" s="60" t="str">
         <f t="shared" si="4"/>
@@ -5712,24 +5648,24 @@
         <v>Local Collector as a Dry Drain or Basin Valve</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="59">
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C35" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C35" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D35" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E35" s="42" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F35" s="42" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G35" s="61" t="s">
         <v>9</v>
@@ -5748,11 +5684,11 @@
       </c>
       <c r="L35" s="33" t="str">
         <f t="shared" si="5"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M35" s="33" t="str">
         <f t="shared" si="6"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N35" s="33" t="str">
         <f t="shared" si="7"/>
@@ -5772,17 +5708,17 @@
         <v>9</v>
       </c>
       <c r="S35" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T35" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U35" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Esgoto.Coletores</v>
       </c>
       <c r="V35" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W35" s="60" t="str">
         <f t="shared" si="4"/>
@@ -5802,21 +5738,21 @@
         <v>Siphoned Collector as a Siphoned Drain</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="59">
         <v>36</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C36" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C36" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D36" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E36" s="42" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F36" s="42" t="s">
         <v>105</v>
@@ -5838,11 +5774,11 @@
       </c>
       <c r="L36" s="33" t="str">
         <f t="shared" si="5"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M36" s="33" t="str">
         <f t="shared" si="6"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N36" s="33" t="str">
         <f t="shared" si="7"/>
@@ -5856,23 +5792,23 @@
         <v>117</v>
       </c>
       <c r="Q36" s="30" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="R36" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S36" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T36" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U36" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Esgoto.Coletores</v>
       </c>
       <c r="V36" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W36" s="60" t="str">
         <f t="shared" si="4"/>
@@ -5892,21 +5828,21 @@
         <v>Floor Horizontal Collection Branch</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="59">
         <v>37</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C37" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C37" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D37" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E37" s="42" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F37" s="42" t="s">
         <v>104</v>
@@ -5928,11 +5864,11 @@
       </c>
       <c r="L37" s="33" t="str">
         <f t="shared" si="5"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M37" s="33" t="str">
         <f t="shared" si="6"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N37" s="33" t="str">
         <f t="shared" si="7"/>
@@ -5946,23 +5882,23 @@
         <v>118</v>
       </c>
       <c r="Q37" s="30" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="R37" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S37" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T37" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U37" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Esgoto.Coletores</v>
       </c>
       <c r="V37" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W37" s="60" t="str">
         <f t="shared" si="4"/>
@@ -5982,21 +5918,21 @@
         <v>Horizontal collection branch of the building</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="59">
         <v>38</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C38" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C38" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D38" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E38" s="42" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F38" s="42" t="s">
         <v>106</v>
@@ -6018,11 +5954,11 @@
       </c>
       <c r="L38" s="33" t="str">
         <f t="shared" ref="L38" si="35">CONCATENATE("", C38)</f>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M38" s="33" t="str">
         <f t="shared" ref="M38" si="36">CONCATENATE("", D38)</f>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N38" s="33" t="str">
         <f t="shared" ref="N38" si="37">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E38),"."," ")," De "," de "))</f>
@@ -6036,23 +5972,23 @@
         <v>119</v>
       </c>
       <c r="Q38" s="30" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="R38" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S38" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T38" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U38" s="30" t="str">
         <f t="shared" ref="U38" si="38">SUBSTITUTE(E38, "_", " ")</f>
         <v>Esgoto.Coletores</v>
       </c>
       <c r="V38" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W38" s="60" t="str">
         <f t="shared" si="4"/>
@@ -6072,24 +6008,24 @@
         <v>Downpipe</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="59">
         <v>39</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C39" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C39" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D39" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E39" s="42" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F39" s="42" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G39" s="61" t="s">
         <v>9</v>
@@ -6108,11 +6044,11 @@
       </c>
       <c r="L39" s="33" t="str">
         <f t="shared" ref="L39" si="39">CONCATENATE("", C39)</f>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M39" s="33" t="str">
         <f t="shared" ref="M39" si="40">CONCATENATE("", D39)</f>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N39" s="33" t="str">
         <f t="shared" ref="N39" si="41">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E39),"."," ")," De "," de "))</f>
@@ -6132,17 +6068,17 @@
         <v>9</v>
       </c>
       <c r="S39" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T39" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U39" s="30" t="str">
         <f t="shared" ref="U39" si="42">SUBSTITUTE(E39, "_", " ")</f>
         <v>Esgoto.Coletores</v>
       </c>
       <c r="V39" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W39" s="60" t="str">
         <f t="shared" si="4"/>
@@ -6162,21 +6098,21 @@
         <v>Siphons</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="59">
         <v>40</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C40" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C40" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D40" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E40" s="42" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F40" s="42" t="s">
         <v>110</v>
@@ -6198,11 +6134,11 @@
       </c>
       <c r="L40" s="33" t="str">
         <f t="shared" ref="L40:L44" si="43">CONCATENATE("", C40)</f>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M40" s="33" t="str">
         <f t="shared" ref="M40:M44" si="44">CONCATENATE("", D40)</f>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N40" s="33" t="str">
         <f t="shared" ref="N40:N44" si="45">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E40),"."," ")," De "," de "))</f>
@@ -6222,17 +6158,17 @@
         <v>9</v>
       </c>
       <c r="S40" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T40" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U40" s="30" t="str">
         <f t="shared" ref="U40:U44" si="46">SUBSTITUTE(E40, "_", " ")</f>
         <v>Esgoto.Visitas</v>
       </c>
       <c r="V40" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W40" s="60" t="str">
         <f t="shared" si="4"/>
@@ -6252,21 +6188,21 @@
         <v>Sandboxes</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="59">
         <v>41</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C41" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C41" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D41" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E41" s="42" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F41" s="42" t="s">
         <v>109</v>
@@ -6288,11 +6224,11 @@
       </c>
       <c r="L41" s="33" t="str">
         <f t="shared" si="43"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M41" s="33" t="str">
         <f t="shared" si="44"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N41" s="33" t="str">
         <f t="shared" si="45"/>
@@ -6312,17 +6248,17 @@
         <v>9</v>
       </c>
       <c r="S41" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T41" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U41" s="30" t="str">
         <f t="shared" si="46"/>
         <v>Esgoto.Visitas</v>
       </c>
       <c r="V41" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W41" s="60" t="str">
         <f t="shared" si="4"/>
@@ -6342,21 +6278,21 @@
         <v>Grease Traps</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="59">
         <v>42</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C42" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C42" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D42" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E42" s="42" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F42" s="42" t="s">
         <v>107</v>
@@ -6378,11 +6314,11 @@
       </c>
       <c r="L42" s="33" t="str">
         <f t="shared" ref="L42:L43" si="47">CONCATENATE("", C42)</f>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M42" s="33" t="str">
         <f t="shared" ref="M42:M43" si="48">CONCATENATE("", D42)</f>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N42" s="33" t="str">
         <f t="shared" ref="N42:N43" si="49">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E42),"."," ")," De "," de "))</f>
@@ -6396,23 +6332,23 @@
         <v>123</v>
       </c>
       <c r="Q42" s="30" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="R42" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S42" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T42" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U42" s="30" t="str">
         <f t="shared" ref="U42:U43" si="50">SUBSTITUTE(E42, "_", " ")</f>
         <v>Esgoto.Visitas</v>
       </c>
       <c r="V42" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W42" s="60" t="str">
         <f t="shared" si="4"/>
@@ -6432,21 +6368,21 @@
         <v>Manholes</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="59">
         <v>43</v>
       </c>
       <c r="B43" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C43" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C43" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D43" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E43" s="42" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F43" s="42" t="s">
         <v>111</v>
@@ -6468,11 +6404,11 @@
       </c>
       <c r="L43" s="33" t="str">
         <f t="shared" si="47"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M43" s="33" t="str">
         <f t="shared" si="48"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N43" s="33" t="str">
         <f t="shared" si="49"/>
@@ -6492,17 +6428,17 @@
         <v>9</v>
       </c>
       <c r="S43" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T43" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U43" s="30" t="str">
         <f t="shared" si="50"/>
         <v>Esgoto.Visitas</v>
       </c>
       <c r="V43" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W43" s="60" t="str">
         <f t="shared" si="4"/>
@@ -6522,21 +6458,21 @@
         <v>Siphon Boxes</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="59">
         <v>44</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C44" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C44" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D44" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E44" s="42" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F44" s="42" t="s">
         <v>108</v>
@@ -6558,11 +6494,11 @@
       </c>
       <c r="L44" s="33" t="str">
         <f t="shared" si="43"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M44" s="33" t="str">
         <f t="shared" si="44"/>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N44" s="33" t="str">
         <f t="shared" si="45"/>
@@ -6582,17 +6518,17 @@
         <v>9</v>
       </c>
       <c r="S44" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T44" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U44" s="30" t="str">
         <f t="shared" si="46"/>
         <v>Esgoto.Visitas</v>
       </c>
       <c r="V44" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W44" s="60" t="str">
         <f t="shared" si="4"/>
@@ -6612,24 +6548,24 @@
         <v>Manholes</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="59">
         <v>45</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C45" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="C45" s="42" t="s">
-        <v>139</v>
-      </c>
       <c r="D45" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E45" s="42" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F45" s="42" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G45" s="61" t="s">
         <v>9</v>
@@ -6648,11 +6584,11 @@
       </c>
       <c r="L45" s="33" t="str">
         <f t="shared" ref="L45" si="51">CONCATENATE("", C45)</f>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M45" s="33" t="str">
         <f t="shared" ref="M45" si="52">CONCATENATE("", D45)</f>
-        <v>Elementos.Hidráulica</v>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N45" s="33" t="str">
         <f t="shared" ref="N45" si="53">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E45),"."," ")," De "," de "))</f>
@@ -6663,36 +6599,36 @@
         <v>Acessório.Sanitário</v>
       </c>
       <c r="P45" s="52" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="Q45" s="52" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="R45" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S45" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T45" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U45" s="30" t="str">
         <f t="shared" ref="U45" si="54">SUBSTITUTE(E45, "_", " ")</f>
         <v>Esgoto.Acessórios</v>
       </c>
       <c r="V45" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W45" s="60" t="str">
         <f t="shared" si="4"/>
         <v>Key-HIDR-45</v>
       </c>
       <c r="X45" s="29" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="Y45" s="29" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="Z45" s="30" t="s">
         <v>133</v>
@@ -6707,76 +6643,71 @@
     <sortCondition ref="F7:F936"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A2:B45">
+    <cfRule type="cellIs" dxfId="31" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="37" priority="1494"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="1494"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F6">
+    <cfRule type="duplicateValues" dxfId="29" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="32" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16">
-    <cfRule type="duplicateValues" dxfId="31" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35">
-    <cfRule type="duplicateValues" dxfId="30" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F38 F40:F1048576 F17:F33 F1 F7:F15">
-    <cfRule type="duplicateValues" dxfId="29" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F46:F1048576">
-    <cfRule type="duplicateValues" dxfId="28" priority="251"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="253"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="1466"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="1487"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="251"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="253"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="1466"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1487"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:O1 A1:D1 Q1:X1">
-    <cfRule type="cellIs" dxfId="24" priority="58" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="58" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P7:P9">
-    <cfRule type="duplicateValues" dxfId="23" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P10:P15 P17:P26">
-    <cfRule type="duplicateValues" dxfId="22" priority="1507"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1507"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P27:P32">
-    <cfRule type="duplicateValues" dxfId="21" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P33">
-    <cfRule type="duplicateValues" dxfId="20" priority="1500"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="1500"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q7:Q9">
-    <cfRule type="duplicateValues" dxfId="19" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q26">
-    <cfRule type="duplicateValues" dxfId="18" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q33">
-    <cfRule type="duplicateValues" dxfId="17" priority="1501"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1501"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1:AA1">
-    <cfRule type="cellIs" dxfId="16" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="23" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA45">
-    <cfRule type="cellIs" dxfId="15" priority="13" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B45">
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
+  <conditionalFormatting sqref="AA2:AA45">
+    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6788,15 +6719,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="9"/>
+    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -6861,7 +6792,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -6926,7 +6857,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -6993,7 +6924,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7009,30 +6940,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S19"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.69140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.3046875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="77.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="77.69140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.53515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.3046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.3828125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="24" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.3046875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.69140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.69140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="14.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
@@ -7091,7 +7022,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="20">
         <v>1</v>
       </c>
@@ -7150,15 +7081,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="20">
         <v>2</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D3" s="50" t="s">
         <v>82</v>
@@ -7170,7 +7101,7 @@
         <v>77</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H3" s="49" t="s">
         <v>77</v>
@@ -7206,18 +7137,18 @@
         <v>9</v>
       </c>
       <c r="S3" s="24" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="20">
         <v>3</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C4" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D4" s="50" t="s">
         <v>82</v>
@@ -7229,7 +7160,7 @@
         <v>77</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H4" s="49" t="s">
         <v>77</v>
@@ -7265,18 +7196,18 @@
         <v>9</v>
       </c>
       <c r="S4" s="24" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="20">
         <v>4</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D5" s="50" t="s">
         <v>82</v>
@@ -7288,7 +7219,7 @@
         <v>77</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H5" s="49" t="s">
         <v>77</v>
@@ -7324,30 +7255,30 @@
         <v>9</v>
       </c>
       <c r="S5" s="24" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="20">
         <v>5</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C6" s="42" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D6" s="50" t="s">
         <v>136</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F6" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H6" s="49" t="s">
         <v>9</v>
@@ -7356,13 +7287,13 @@
         <v>9</v>
       </c>
       <c r="J6" s="49" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="K6" s="24" t="s">
         <v>134</v>
       </c>
       <c r="L6" s="49" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="M6" s="24" t="s">
         <v>101</v>
@@ -7377,36 +7308,36 @@
         <v>102</v>
       </c>
       <c r="Q6" s="24" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R6" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S6" s="24" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="20">
         <v>6</v>
       </c>
       <c r="B7" s="47" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C7" s="42" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D7" s="50" t="s">
         <v>136</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F7" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H7" s="49" t="s">
         <v>9</v>
@@ -7415,13 +7346,13 @@
         <v>9</v>
       </c>
       <c r="J7" s="49" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="K7" s="24" t="s">
         <v>134</v>
       </c>
       <c r="L7" s="49" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="M7" s="24" t="s">
         <v>101</v>
@@ -7436,36 +7367,36 @@
         <v>102</v>
       </c>
       <c r="Q7" s="24" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R7" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S7" s="24" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="20">
         <v>7</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C8" s="42" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D8" s="50" t="s">
         <v>136</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F8" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H8" s="49" t="s">
         <v>9</v>
@@ -7474,13 +7405,13 @@
         <v>9</v>
       </c>
       <c r="J8" s="49" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="K8" s="24" t="s">
         <v>134</v>
       </c>
       <c r="L8" s="49" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="M8" s="24" t="s">
         <v>101</v>
@@ -7489,42 +7420,42 @@
         <v>100</v>
       </c>
       <c r="O8" s="24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P8" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q8" s="24" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R8" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S8" s="24" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="20">
         <v>8</v>
       </c>
       <c r="B9" s="47" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C9" s="42" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" s="50" t="s">
         <v>136</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F9" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H9" s="49" t="s">
         <v>9</v>
@@ -7533,13 +7464,13 @@
         <v>9</v>
       </c>
       <c r="J9" s="49" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="K9" s="24" t="s">
         <v>134</v>
       </c>
       <c r="L9" s="49" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="M9" s="24" t="s">
         <v>101</v>
@@ -7548,42 +7479,42 @@
         <v>100</v>
       </c>
       <c r="O9" s="24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P9" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q9" s="24" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R9" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S9" s="24" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="20">
         <v>9</v>
       </c>
       <c r="B10" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C10" s="42" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D10" s="50" t="s">
         <v>136</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F10" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H10" s="49" t="s">
         <v>9</v>
@@ -7592,13 +7523,13 @@
         <v>9</v>
       </c>
       <c r="J10" s="49" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="K10" s="24" t="s">
         <v>134</v>
       </c>
       <c r="L10" s="49" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="M10" s="24" t="s">
         <v>101</v>
@@ -7607,42 +7538,42 @@
         <v>100</v>
       </c>
       <c r="O10" s="24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P10" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q10" s="24" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R10" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S10" s="24" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="20">
         <v>10</v>
       </c>
       <c r="B11" s="47" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C11" s="42" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D11" s="50" t="s">
         <v>136</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F11" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H11" s="49" t="s">
         <v>9</v>
@@ -7651,13 +7582,13 @@
         <v>9</v>
       </c>
       <c r="J11" s="49" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="K11" s="24" t="s">
         <v>134</v>
       </c>
       <c r="L11" s="49" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="M11" s="24" t="s">
         <v>101</v>
@@ -7666,42 +7597,42 @@
         <v>100</v>
       </c>
       <c r="O11" s="24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P11" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q11" s="24" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R11" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S11" s="24" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="20">
         <v>11</v>
       </c>
       <c r="B12" s="47" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C12" s="42" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D12" s="50" t="s">
         <v>136</v>
       </c>
       <c r="E12" s="34" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F12" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H12" s="49" t="s">
         <v>9</v>
@@ -7710,13 +7641,13 @@
         <v>9</v>
       </c>
       <c r="J12" s="49" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="K12" s="24" t="s">
         <v>134</v>
       </c>
       <c r="L12" s="49" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="M12" s="24" t="s">
         <v>101</v>
@@ -7725,42 +7656,42 @@
         <v>100</v>
       </c>
       <c r="O12" s="24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P12" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q12" s="24" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R12" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S12" s="24" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="20">
         <v>12</v>
       </c>
       <c r="B13" s="47" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C13" s="42" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D13" s="50" t="s">
         <v>136</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F13" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H13" s="49" t="s">
         <v>9</v>
@@ -7769,13 +7700,13 @@
         <v>9</v>
       </c>
       <c r="J13" s="49" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="K13" s="24" t="s">
         <v>134</v>
       </c>
       <c r="L13" s="49" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="M13" s="24" t="s">
         <v>101</v>
@@ -7784,42 +7715,42 @@
         <v>100</v>
       </c>
       <c r="O13" s="24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P13" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q13" s="24" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R13" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S13" s="24" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="20">
         <v>13</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C14" s="42" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D14" s="50" t="s">
         <v>136</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F14" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H14" s="49" t="s">
         <v>9</v>
@@ -7828,13 +7759,13 @@
         <v>9</v>
       </c>
       <c r="J14" s="49" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="K14" s="24" t="s">
         <v>134</v>
       </c>
       <c r="L14" s="49" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="M14" s="24" t="s">
         <v>101</v>
@@ -7843,42 +7774,42 @@
         <v>100</v>
       </c>
       <c r="O14" s="24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P14" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q14" s="24" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R14" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S14" s="24" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="20">
         <v>14</v>
       </c>
       <c r="B15" s="47" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C15" s="42" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D15" s="50" t="s">
         <v>136</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F15" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H15" s="49" t="s">
         <v>9</v>
@@ -7887,13 +7818,13 @@
         <v>9</v>
       </c>
       <c r="J15" s="49" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="K15" s="24" t="s">
         <v>134</v>
       </c>
       <c r="L15" s="49" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="M15" s="24" t="s">
         <v>101</v>
@@ -7902,42 +7833,42 @@
         <v>100</v>
       </c>
       <c r="O15" s="24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P15" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q15" s="24" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R15" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S15" s="24" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="20">
         <v>15</v>
       </c>
       <c r="B16" s="47" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C16" s="42" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D16" s="50" t="s">
         <v>136</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F16" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H16" s="49" t="s">
         <v>9</v>
@@ -7946,13 +7877,13 @@
         <v>9</v>
       </c>
       <c r="J16" s="49" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="K16" s="24" t="s">
         <v>134</v>
       </c>
       <c r="L16" s="49" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="M16" s="24" t="s">
         <v>101</v>
@@ -7961,42 +7892,42 @@
         <v>100</v>
       </c>
       <c r="O16" s="24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P16" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q16" s="24" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R16" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S16" s="24" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="20">
         <v>16</v>
       </c>
       <c r="B17" s="47" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C17" s="42" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D17" s="50" t="s">
         <v>136</v>
       </c>
       <c r="E17" s="34" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F17" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H17" s="49" t="s">
         <v>9</v>
@@ -8005,13 +7936,13 @@
         <v>9</v>
       </c>
       <c r="J17" s="49" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="K17" s="24" t="s">
         <v>134</v>
       </c>
       <c r="L17" s="49" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="M17" s="24" t="s">
         <v>101</v>
@@ -8020,42 +7951,42 @@
         <v>100</v>
       </c>
       <c r="O17" s="24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P17" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q17" s="24" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R17" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S17" s="24" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="20">
         <v>17</v>
       </c>
       <c r="B18" s="47" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C18" s="42" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D18" s="50" t="s">
         <v>136</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F18" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H18" s="49" t="s">
         <v>9</v>
@@ -8064,13 +7995,13 @@
         <v>9</v>
       </c>
       <c r="J18" s="49" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="K18" s="24" t="s">
         <v>134</v>
       </c>
       <c r="L18" s="49" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="M18" s="24" t="s">
         <v>101</v>
@@ -8079,42 +8010,42 @@
         <v>100</v>
       </c>
       <c r="O18" s="24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P18" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q18" s="24" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R18" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S18" s="24" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="20">
         <v>18</v>
       </c>
       <c r="B19" s="47" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C19" s="42" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D19" s="50" t="s">
         <v>136</v>
       </c>
       <c r="E19" s="34" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F19" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G19" s="23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H19" s="49" t="s">
         <v>9</v>
@@ -8123,13 +8054,13 @@
         <v>9</v>
       </c>
       <c r="J19" s="49" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="K19" s="24" t="s">
         <v>134</v>
       </c>
       <c r="L19" s="49" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="M19" s="24" t="s">
         <v>101</v>
@@ -8138,25 +8069,25 @@
         <v>100</v>
       </c>
       <c r="O19" s="24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P19" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q19" s="24" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R19" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S19" s="24" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3:C5">
-    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8166,15 +8097,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.15234375" style="26" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -8197,7 +8128,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -8226,22 +8157,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="11" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
